--- a/Excel/PracticeExcel/02Functions_Formulas/sample-data-fx.blank.xlsx
+++ b/Excel/PracticeExcel/02Functions_Formulas/sample-data-fx.blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Documents\PythonClassSF\DataAnalytics01\Excel\02Functions_Formulas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF60EF9A-8E98-425F-BFB5-280FCDC9DB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F724FB2C-EACB-470B-9067-2343E8D16EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="Task 03" sheetId="5" r:id="rId5"/>
     <sheet name="Task 04" sheetId="6" r:id="rId6"/>
     <sheet name="Task 05" sheetId="7" r:id="rId7"/>
+    <sheet name="Task 06" sheetId="8" r:id="rId8"/>
+    <sheet name="Task 07" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="787">
   <si>
     <t>Essential Excel Functions &amp; Formulas</t>
   </si>
@@ -2404,6 +2406,27 @@
   </si>
   <si>
     <t>Count:</t>
+  </si>
+  <si>
+    <t>Employee Id</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Last name</t>
+  </si>
+  <si>
+    <t>Entire Data horizantally</t>
+  </si>
+  <si>
+    <t>Entire Data Vertically</t>
+  </si>
+  <si>
+    <t>Entire All Data Get by last name using Filter</t>
   </si>
 </sst>
 </file>
@@ -2466,7 +2489,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2500,6 +2523,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2554,7 +2583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2633,6 +2662,11 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2676,8 +2710,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="">
@@ -2696,7 +2730,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="">
@@ -2751,6 +2785,7 @@
           <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
         </inkml:channelProperties>
       </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-05-22T01:50:00.741"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.1" units="cm"/>
@@ -2763,7 +2798,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}" name="staff" displayName="staff" ref="C7:O267" totalsRowShown="0">
-  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}"/>
+  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Tuxwell"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:O267">
     <sortCondition ref="C7:C267"/>
   </sortState>
@@ -4616,7 +4657,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" hidden="1">
       <c r="C8" t="s">
         <v>42</v>
       </c>
@@ -4657,7 +4698,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" hidden="1">
       <c r="C9" t="s">
         <v>51</v>
       </c>
@@ -4780,7 +4821,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" hidden="1">
       <c r="C12" t="s">
         <v>61</v>
       </c>
@@ -4821,7 +4862,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" hidden="1">
       <c r="C13" t="s">
         <v>68</v>
       </c>
@@ -4862,7 +4903,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" hidden="1">
       <c r="C14" t="s">
         <v>72</v>
       </c>
@@ -4903,7 +4944,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" hidden="1">
       <c r="C15" t="s">
         <v>75</v>
       </c>
@@ -4944,7 +4985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" hidden="1">
       <c r="C16" t="s">
         <v>79</v>
       </c>
@@ -4985,7 +5026,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:15">
+    <row r="17" spans="3:15" hidden="1">
       <c r="C17" t="s">
         <v>83</v>
       </c>
@@ -5026,7 +5067,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="3:15">
+    <row r="18" spans="3:15" hidden="1">
       <c r="C18" t="s">
         <v>87</v>
       </c>
@@ -5067,7 +5108,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="3:15">
+    <row r="19" spans="3:15" hidden="1">
       <c r="C19" t="s">
         <v>90</v>
       </c>
@@ -5108,7 +5149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:15">
+    <row r="20" spans="3:15" hidden="1">
       <c r="C20" t="s">
         <v>94</v>
       </c>
@@ -5149,7 +5190,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="3:15">
+    <row r="21" spans="3:15" hidden="1">
       <c r="C21" t="s">
         <v>98</v>
       </c>
@@ -5190,7 +5231,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:15">
+    <row r="22" spans="3:15" hidden="1">
       <c r="C22" t="s">
         <v>102</v>
       </c>
@@ -5231,7 +5272,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="3:15">
+    <row r="23" spans="3:15" hidden="1">
       <c r="C23" t="s">
         <v>106</v>
       </c>
@@ -5272,7 +5313,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="3:15">
+    <row r="24" spans="3:15" hidden="1">
       <c r="C24" t="s">
         <v>110</v>
       </c>
@@ -5313,7 +5354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="3:15">
+    <row r="25" spans="3:15" hidden="1">
       <c r="C25" t="s">
         <v>113</v>
       </c>
@@ -5354,7 +5395,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:15">
+    <row r="26" spans="3:15" hidden="1">
       <c r="C26" t="s">
         <v>117</v>
       </c>
@@ -5395,7 +5436,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="3:15">
+    <row r="27" spans="3:15" hidden="1">
       <c r="C27" t="s">
         <v>120</v>
       </c>
@@ -5436,7 +5477,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="3:15">
+    <row r="28" spans="3:15" hidden="1">
       <c r="C28" t="s">
         <v>124</v>
       </c>
@@ -5477,7 +5518,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="3:15">
+    <row r="29" spans="3:15" hidden="1">
       <c r="C29" t="s">
         <v>127</v>
       </c>
@@ -5518,7 +5559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="3:15">
+    <row r="30" spans="3:15" hidden="1">
       <c r="C30" t="s">
         <v>130</v>
       </c>
@@ -5559,7 +5600,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="3:15">
+    <row r="31" spans="3:15" hidden="1">
       <c r="C31" t="s">
         <v>133</v>
       </c>
@@ -5600,7 +5641,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="3:15">
+    <row r="32" spans="3:15" hidden="1">
       <c r="C32" t="s">
         <v>133</v>
       </c>
@@ -5641,7 +5682,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="3:15">
+    <row r="33" spans="3:15" hidden="1">
       <c r="C33" t="s">
         <v>136</v>
       </c>
@@ -5682,7 +5723,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:15">
+    <row r="34" spans="3:15" hidden="1">
       <c r="C34" t="s">
         <v>139</v>
       </c>
@@ -5723,7 +5764,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="3:15">
+    <row r="35" spans="3:15" hidden="1">
       <c r="C35" t="s">
         <v>142</v>
       </c>
@@ -5764,7 +5805,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="3:15">
+    <row r="36" spans="3:15" hidden="1">
       <c r="C36" t="s">
         <v>146</v>
       </c>
@@ -5805,7 +5846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:15">
+    <row r="37" spans="3:15" hidden="1">
       <c r="C37" t="s">
         <v>149</v>
       </c>
@@ -5846,7 +5887,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="3:15">
+    <row r="38" spans="3:15" hidden="1">
       <c r="C38" t="s">
         <v>152</v>
       </c>
@@ -5887,7 +5928,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="3:15">
+    <row r="39" spans="3:15" hidden="1">
       <c r="C39" t="s">
         <v>156</v>
       </c>
@@ -5928,7 +5969,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="3:15">
+    <row r="40" spans="3:15" hidden="1">
       <c r="C40" t="s">
         <v>159</v>
       </c>
@@ -5969,7 +6010,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="3:15">
+    <row r="41" spans="3:15" hidden="1">
       <c r="C41" t="s">
         <v>162</v>
       </c>
@@ -6010,7 +6051,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="3:15">
+    <row r="42" spans="3:15" hidden="1">
       <c r="C42" t="s">
         <v>165</v>
       </c>
@@ -6051,7 +6092,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="3:15">
+    <row r="43" spans="3:15" hidden="1">
       <c r="C43" t="s">
         <v>168</v>
       </c>
@@ -6092,7 +6133,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="3:15">
+    <row r="44" spans="3:15" hidden="1">
       <c r="C44" t="s">
         <v>171</v>
       </c>
@@ -6133,7 +6174,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="3:15">
+    <row r="45" spans="3:15" hidden="1">
       <c r="C45" t="s">
         <v>174</v>
       </c>
@@ -6174,7 +6215,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="3:15">
+    <row r="46" spans="3:15" hidden="1">
       <c r="C46" t="s">
         <v>177</v>
       </c>
@@ -6215,7 +6256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="3:15">
+    <row r="47" spans="3:15" hidden="1">
       <c r="C47" t="s">
         <v>180</v>
       </c>
@@ -6256,7 +6297,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="3:15">
+    <row r="48" spans="3:15" hidden="1">
       <c r="C48" t="s">
         <v>183</v>
       </c>
@@ -6297,7 +6338,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="3:15">
+    <row r="49" spans="3:15" hidden="1">
       <c r="C49" t="s">
         <v>186</v>
       </c>
@@ -6338,7 +6379,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="3:15">
+    <row r="50" spans="3:15" hidden="1">
       <c r="C50" t="s">
         <v>189</v>
       </c>
@@ -6379,7 +6420,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="3:15">
+    <row r="51" spans="3:15" hidden="1">
       <c r="C51" t="s">
         <v>192</v>
       </c>
@@ -6420,7 +6461,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="3:15">
+    <row r="52" spans="3:15" hidden="1">
       <c r="C52" t="s">
         <v>192</v>
       </c>
@@ -6461,7 +6502,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="3:15">
+    <row r="53" spans="3:15" hidden="1">
       <c r="C53" t="s">
         <v>197</v>
       </c>
@@ -6502,7 +6543,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="3:15">
+    <row r="54" spans="3:15" hidden="1">
       <c r="C54" t="s">
         <v>200</v>
       </c>
@@ -6543,7 +6584,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="3:15">
+    <row r="55" spans="3:15" hidden="1">
       <c r="C55" t="s">
         <v>203</v>
       </c>
@@ -6584,7 +6625,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="3:15">
+    <row r="56" spans="3:15" hidden="1">
       <c r="C56" t="s">
         <v>206</v>
       </c>
@@ -6666,7 +6707,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="3:15">
+    <row r="58" spans="3:15" hidden="1">
       <c r="C58" t="s">
         <v>210</v>
       </c>
@@ -6707,7 +6748,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="3:15">
+    <row r="59" spans="3:15" hidden="1">
       <c r="C59" t="s">
         <v>213</v>
       </c>
@@ -6748,7 +6789,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="3:15">
+    <row r="60" spans="3:15" hidden="1">
       <c r="C60" t="s">
         <v>216</v>
       </c>
@@ -6789,7 +6830,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="3:15">
+    <row r="61" spans="3:15" hidden="1">
       <c r="C61" t="s">
         <v>220</v>
       </c>
@@ -6830,7 +6871,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="3:15">
+    <row r="62" spans="3:15" hidden="1">
       <c r="C62" t="s">
         <v>223</v>
       </c>
@@ -6871,7 +6912,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="3:15">
+    <row r="63" spans="3:15" hidden="1">
       <c r="C63" t="s">
         <v>226</v>
       </c>
@@ -6912,7 +6953,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="3:15">
+    <row r="64" spans="3:15" hidden="1">
       <c r="C64" t="s">
         <v>229</v>
       </c>
@@ -6953,7 +6994,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="3:15">
+    <row r="65" spans="3:15" hidden="1">
       <c r="C65" t="s">
         <v>232</v>
       </c>
@@ -6994,7 +7035,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="3:15">
+    <row r="66" spans="3:15" hidden="1">
       <c r="C66" t="s">
         <v>235</v>
       </c>
@@ -7035,7 +7076,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="3:15">
+    <row r="67" spans="3:15" hidden="1">
       <c r="C67" t="s">
         <v>238</v>
       </c>
@@ -7076,7 +7117,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="3:15">
+    <row r="68" spans="3:15" hidden="1">
       <c r="C68" t="s">
         <v>241</v>
       </c>
@@ -7117,7 +7158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="3:15">
+    <row r="69" spans="3:15" hidden="1">
       <c r="C69" t="s">
         <v>244</v>
       </c>
@@ -7158,7 +7199,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="3:15">
+    <row r="70" spans="3:15" hidden="1">
       <c r="C70" t="s">
         <v>247</v>
       </c>
@@ -7199,7 +7240,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="3:15">
+    <row r="71" spans="3:15" hidden="1">
       <c r="C71" t="s">
         <v>248</v>
       </c>
@@ -7240,7 +7281,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="3:15">
+    <row r="72" spans="3:15" hidden="1">
       <c r="C72" t="s">
         <v>251</v>
       </c>
@@ -7281,7 +7322,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="3:15">
+    <row r="73" spans="3:15" hidden="1">
       <c r="C73" t="s">
         <v>254</v>
       </c>
@@ -7322,7 +7363,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="3:15">
+    <row r="74" spans="3:15" hidden="1">
       <c r="C74" t="s">
         <v>257</v>
       </c>
@@ -7363,7 +7404,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="3:15">
+    <row r="75" spans="3:15" hidden="1">
       <c r="C75" t="s">
         <v>260</v>
       </c>
@@ -7404,7 +7445,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="3:15">
+    <row r="76" spans="3:15" hidden="1">
       <c r="C76" t="s">
         <v>260</v>
       </c>
@@ -7445,7 +7486,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="3:15">
+    <row r="77" spans="3:15" hidden="1">
       <c r="C77" t="s">
         <v>265</v>
       </c>
@@ -7486,7 +7527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="3:15">
+    <row r="78" spans="3:15" hidden="1">
       <c r="C78" t="s">
         <v>268</v>
       </c>
@@ -7527,7 +7568,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="3:15">
+    <row r="79" spans="3:15" hidden="1">
       <c r="C79" t="s">
         <v>271</v>
       </c>
@@ -7568,7 +7609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="3:15">
+    <row r="80" spans="3:15" hidden="1">
       <c r="C80" t="s">
         <v>274</v>
       </c>
@@ -7609,7 +7650,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="3:15">
+    <row r="81" spans="3:15" hidden="1">
       <c r="C81" t="s">
         <v>277</v>
       </c>
@@ -7650,7 +7691,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="3:15">
+    <row r="82" spans="3:15" hidden="1">
       <c r="C82" t="s">
         <v>280</v>
       </c>
@@ -7691,7 +7732,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="3:15">
+    <row r="83" spans="3:15" hidden="1">
       <c r="C83" t="s">
         <v>283</v>
       </c>
@@ -7732,7 +7773,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="3:15">
+    <row r="84" spans="3:15" hidden="1">
       <c r="C84" t="s">
         <v>286</v>
       </c>
@@ -7773,7 +7814,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="3:15">
+    <row r="85" spans="3:15" hidden="1">
       <c r="C85" t="s">
         <v>289</v>
       </c>
@@ -7814,7 +7855,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="3:15">
+    <row r="86" spans="3:15" hidden="1">
       <c r="C86" t="s">
         <v>292</v>
       </c>
@@ -7855,7 +7896,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="3:15">
+    <row r="87" spans="3:15" hidden="1">
       <c r="C87" t="s">
         <v>295</v>
       </c>
@@ -7896,7 +7937,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="88" spans="3:15">
+    <row r="88" spans="3:15" hidden="1">
       <c r="C88" t="s">
         <v>298</v>
       </c>
@@ -7937,7 +7978,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="89" spans="3:15">
+    <row r="89" spans="3:15" hidden="1">
       <c r="C89" t="s">
         <v>301</v>
       </c>
@@ -7978,7 +8019,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="3:15">
+    <row r="90" spans="3:15" hidden="1">
       <c r="C90" t="s">
         <v>304</v>
       </c>
@@ -8019,7 +8060,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="91" spans="3:15">
+    <row r="91" spans="3:15" hidden="1">
       <c r="C91" t="s">
         <v>304</v>
       </c>
@@ -8060,7 +8101,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="3:15">
+    <row r="92" spans="3:15" hidden="1">
       <c r="C92" t="s">
         <v>309</v>
       </c>
@@ -8101,7 +8142,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="3:15">
+    <row r="93" spans="3:15" hidden="1">
       <c r="C93" t="s">
         <v>309</v>
       </c>
@@ -8142,7 +8183,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="3:15">
+    <row r="94" spans="3:15" hidden="1">
       <c r="C94" t="s">
         <v>312</v>
       </c>
@@ -8183,7 +8224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="3:15">
+    <row r="95" spans="3:15" hidden="1">
       <c r="C95" t="s">
         <v>315</v>
       </c>
@@ -8224,7 +8265,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="3:15">
+    <row r="96" spans="3:15" hidden="1">
       <c r="C96" t="s">
         <v>318</v>
       </c>
@@ -8265,7 +8306,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="3:15">
+    <row r="97" spans="3:15" hidden="1">
       <c r="C97" t="s">
         <v>321</v>
       </c>
@@ -8306,7 +8347,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="3:15">
+    <row r="98" spans="3:15" hidden="1">
       <c r="C98" t="s">
         <v>324</v>
       </c>
@@ -8347,7 +8388,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="3:15">
+    <row r="99" spans="3:15" hidden="1">
       <c r="C99" t="s">
         <v>327</v>
       </c>
@@ -8388,7 +8429,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="3:15">
+    <row r="100" spans="3:15" hidden="1">
       <c r="C100" t="s">
         <v>330</v>
       </c>
@@ -8429,7 +8470,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="3:15">
+    <row r="101" spans="3:15" hidden="1">
       <c r="C101" t="s">
         <v>333</v>
       </c>
@@ -8470,7 +8511,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="3:15">
+    <row r="102" spans="3:15" hidden="1">
       <c r="C102" t="s">
         <v>333</v>
       </c>
@@ -8511,7 +8552,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" spans="3:15">
+    <row r="103" spans="3:15" hidden="1">
       <c r="C103" t="s">
         <v>336</v>
       </c>
@@ -8552,7 +8593,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="3:15">
+    <row r="104" spans="3:15" hidden="1">
       <c r="C104" t="s">
         <v>339</v>
       </c>
@@ -8593,7 +8634,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="3:15">
+    <row r="105" spans="3:15" hidden="1">
       <c r="C105" t="s">
         <v>342</v>
       </c>
@@ -8634,7 +8675,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="106" spans="3:15">
+    <row r="106" spans="3:15" hidden="1">
       <c r="C106" t="s">
         <v>345</v>
       </c>
@@ -8675,7 +8716,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="3:15">
+    <row r="107" spans="3:15" hidden="1">
       <c r="C107" t="s">
         <v>348</v>
       </c>
@@ -8716,7 +8757,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="3:15">
+    <row r="108" spans="3:15" hidden="1">
       <c r="C108" t="s">
         <v>351</v>
       </c>
@@ -8757,7 +8798,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="3:15">
+    <row r="109" spans="3:15" hidden="1">
       <c r="C109" t="s">
         <v>354</v>
       </c>
@@ -8798,7 +8839,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="3:15">
+    <row r="110" spans="3:15" hidden="1">
       <c r="C110" t="s">
         <v>354</v>
       </c>
@@ -8839,7 +8880,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="111" spans="3:15">
+    <row r="111" spans="3:15" hidden="1">
       <c r="C111" t="s">
         <v>357</v>
       </c>
@@ -8880,7 +8921,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="3:15">
+    <row r="112" spans="3:15" hidden="1">
       <c r="C112" t="s">
         <v>360</v>
       </c>
@@ -8921,7 +8962,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="3:15">
+    <row r="113" spans="3:15" hidden="1">
       <c r="C113" t="s">
         <v>363</v>
       </c>
@@ -8962,7 +9003,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="3:15">
+    <row r="114" spans="3:15" hidden="1">
       <c r="C114" t="s">
         <v>366</v>
       </c>
@@ -9003,7 +9044,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="3:15">
+    <row r="115" spans="3:15" hidden="1">
       <c r="C115" t="s">
         <v>366</v>
       </c>
@@ -9044,7 +9085,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" spans="3:15">
+    <row r="116" spans="3:15" hidden="1">
       <c r="C116" t="s">
         <v>369</v>
       </c>
@@ -9085,7 +9126,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="3:15">
+    <row r="117" spans="3:15" hidden="1">
       <c r="C117" t="s">
         <v>372</v>
       </c>
@@ -9126,7 +9167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="3:15">
+    <row r="118" spans="3:15" hidden="1">
       <c r="C118" t="s">
         <v>375</v>
       </c>
@@ -9167,7 +9208,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="119" spans="3:15">
+    <row r="119" spans="3:15" hidden="1">
       <c r="C119" t="s">
         <v>378</v>
       </c>
@@ -9208,7 +9249,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="3:15">
+    <row r="120" spans="3:15" hidden="1">
       <c r="C120" t="s">
         <v>381</v>
       </c>
@@ -9249,7 +9290,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="3:15">
+    <row r="121" spans="3:15" hidden="1">
       <c r="C121" t="s">
         <v>384</v>
       </c>
@@ -9290,7 +9331,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="3:15">
+    <row r="122" spans="3:15" hidden="1">
       <c r="C122" t="s">
         <v>387</v>
       </c>
@@ -9331,7 +9372,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="3:15">
+    <row r="123" spans="3:15" hidden="1">
       <c r="C123" t="s">
         <v>390</v>
       </c>
@@ -9372,7 +9413,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="3:15">
+    <row r="124" spans="3:15" hidden="1">
       <c r="C124" t="s">
         <v>393</v>
       </c>
@@ -9413,7 +9454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125" spans="3:15">
+    <row r="125" spans="3:15" hidden="1">
       <c r="C125" t="s">
         <v>396</v>
       </c>
@@ -9454,7 +9495,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="126" spans="3:15">
+    <row r="126" spans="3:15" hidden="1">
       <c r="C126" t="s">
         <v>399</v>
       </c>
@@ -9495,7 +9536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="3:15">
+    <row r="127" spans="3:15" hidden="1">
       <c r="C127" t="s">
         <v>402</v>
       </c>
@@ -9536,7 +9577,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="3:15">
+    <row r="128" spans="3:15" hidden="1">
       <c r="C128" t="s">
         <v>405</v>
       </c>
@@ -9577,7 +9618,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="129" spans="3:15">
+    <row r="129" spans="3:15" hidden="1">
       <c r="C129" t="s">
         <v>408</v>
       </c>
@@ -9618,7 +9659,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="3:15">
+    <row r="130" spans="3:15" hidden="1">
       <c r="C130" t="s">
         <v>411</v>
       </c>
@@ -9659,7 +9700,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="3:15">
+    <row r="131" spans="3:15" hidden="1">
       <c r="C131" t="s">
         <v>414</v>
       </c>
@@ -9700,7 +9741,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="3:15">
+    <row r="132" spans="3:15" hidden="1">
       <c r="C132" t="s">
         <v>417</v>
       </c>
@@ -9741,7 +9782,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="3:15">
+    <row r="133" spans="3:15" hidden="1">
       <c r="C133" t="s">
         <v>420</v>
       </c>
@@ -9782,7 +9823,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="134" spans="3:15">
+    <row r="134" spans="3:15" hidden="1">
       <c r="C134" t="s">
         <v>420</v>
       </c>
@@ -9823,7 +9864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="3:15">
+    <row r="135" spans="3:15" hidden="1">
       <c r="C135" t="s">
         <v>425</v>
       </c>
@@ -9864,7 +9905,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="3:15">
+    <row r="136" spans="3:15" hidden="1">
       <c r="C136" t="s">
         <v>428</v>
       </c>
@@ -9905,7 +9946,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="137" spans="3:15">
+    <row r="137" spans="3:15" hidden="1">
       <c r="C137" t="s">
         <v>431</v>
       </c>
@@ -9946,7 +9987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="138" spans="3:15">
+    <row r="138" spans="3:15" hidden="1">
       <c r="C138" t="s">
         <v>434</v>
       </c>
@@ -9987,7 +10028,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="3:15">
+    <row r="139" spans="3:15" hidden="1">
       <c r="C139" t="s">
         <v>437</v>
       </c>
@@ -10028,7 +10069,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="3:15">
+    <row r="140" spans="3:15" hidden="1">
       <c r="C140" t="s">
         <v>440</v>
       </c>
@@ -10069,7 +10110,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="3:15">
+    <row r="141" spans="3:15" hidden="1">
       <c r="C141" t="s">
         <v>443</v>
       </c>
@@ -10110,7 +10151,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="3:15">
+    <row r="142" spans="3:15" hidden="1">
       <c r="C142" t="s">
         <v>446</v>
       </c>
@@ -10151,7 +10192,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="3:15">
+    <row r="143" spans="3:15" hidden="1">
       <c r="C143" t="s">
         <v>446</v>
       </c>
@@ -10192,7 +10233,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="3:15">
+    <row r="144" spans="3:15" hidden="1">
       <c r="C144" t="s">
         <v>449</v>
       </c>
@@ -10233,7 +10274,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="3:15">
+    <row r="145" spans="3:15" hidden="1">
       <c r="C145" t="s">
         <v>452</v>
       </c>
@@ -10274,7 +10315,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="146" spans="3:15">
+    <row r="146" spans="3:15" hidden="1">
       <c r="C146" t="s">
         <v>455</v>
       </c>
@@ -10315,7 +10356,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="3:15">
+    <row r="147" spans="3:15" hidden="1">
       <c r="C147" t="s">
         <v>458</v>
       </c>
@@ -10356,7 +10397,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="148" spans="3:15">
+    <row r="148" spans="3:15" hidden="1">
       <c r="C148" t="s">
         <v>458</v>
       </c>
@@ -10397,7 +10438,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="149" spans="3:15">
+    <row r="149" spans="3:15" hidden="1">
       <c r="C149" t="s">
         <v>463</v>
       </c>
@@ -10438,7 +10479,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="3:15">
+    <row r="150" spans="3:15" hidden="1">
       <c r="C150" t="s">
         <v>466</v>
       </c>
@@ -10479,7 +10520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="3:15">
+    <row r="151" spans="3:15" hidden="1">
       <c r="C151" t="s">
         <v>469</v>
       </c>
@@ -10520,7 +10561,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="3:15">
+    <row r="152" spans="3:15" hidden="1">
       <c r="C152" t="s">
         <v>472</v>
       </c>
@@ -10561,7 +10602,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="3:15">
+    <row r="153" spans="3:15" hidden="1">
       <c r="C153" t="s">
         <v>475</v>
       </c>
@@ -10602,7 +10643,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="3:15">
+    <row r="154" spans="3:15" hidden="1">
       <c r="C154" t="s">
         <v>475</v>
       </c>
@@ -10643,7 +10684,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="3:15">
+    <row r="155" spans="3:15" hidden="1">
       <c r="C155" t="s">
         <v>478</v>
       </c>
@@ -10684,7 +10725,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="3:15">
+    <row r="156" spans="3:15" hidden="1">
       <c r="C156" t="s">
         <v>481</v>
       </c>
@@ -10725,7 +10766,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="3:15">
+    <row r="157" spans="3:15" hidden="1">
       <c r="C157" t="s">
         <v>484</v>
       </c>
@@ -10766,7 +10807,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="3:15">
+    <row r="158" spans="3:15" hidden="1">
       <c r="C158" t="s">
         <v>484</v>
       </c>
@@ -10807,7 +10848,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="3:15">
+    <row r="159" spans="3:15" hidden="1">
       <c r="C159" t="s">
         <v>487</v>
       </c>
@@ -10848,7 +10889,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="3:15">
+    <row r="160" spans="3:15" hidden="1">
       <c r="C160" t="s">
         <v>490</v>
       </c>
@@ -10889,7 +10930,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="3:15">
+    <row r="161" spans="3:15" hidden="1">
       <c r="C161" t="s">
         <v>491</v>
       </c>
@@ -10930,7 +10971,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="3:15">
+    <row r="162" spans="3:15" hidden="1">
       <c r="C162" t="s">
         <v>494</v>
       </c>
@@ -10971,7 +11012,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="3:15">
+    <row r="163" spans="3:15" hidden="1">
       <c r="C163" t="s">
         <v>497</v>
       </c>
@@ -11012,7 +11053,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="3:15">
+    <row r="164" spans="3:15" hidden="1">
       <c r="C164" t="s">
         <v>500</v>
       </c>
@@ -11053,7 +11094,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="165" spans="3:15">
+    <row r="165" spans="3:15" hidden="1">
       <c r="C165" t="s">
         <v>503</v>
       </c>
@@ -11094,7 +11135,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166" spans="3:15">
+    <row r="166" spans="3:15" hidden="1">
       <c r="C166" t="s">
         <v>503</v>
       </c>
@@ -11135,7 +11176,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="3:15">
+    <row r="167" spans="3:15" hidden="1">
       <c r="C167" t="s">
         <v>506</v>
       </c>
@@ -11176,7 +11217,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="168" spans="3:15">
+    <row r="168" spans="3:15" hidden="1">
       <c r="C168" t="s">
         <v>506</v>
       </c>
@@ -11217,7 +11258,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="169" spans="3:15">
+    <row r="169" spans="3:15" hidden="1">
       <c r="C169" t="s">
         <v>509</v>
       </c>
@@ -11258,7 +11299,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" spans="3:15">
+    <row r="170" spans="3:15" hidden="1">
       <c r="C170" t="s">
         <v>512</v>
       </c>
@@ -11299,7 +11340,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="3:15">
+    <row r="171" spans="3:15" hidden="1">
       <c r="C171" t="s">
         <v>515</v>
       </c>
@@ -11340,7 +11381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="3:15">
+    <row r="172" spans="3:15" hidden="1">
       <c r="C172" t="s">
         <v>518</v>
       </c>
@@ -11381,7 +11422,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="173" spans="3:15">
+    <row r="173" spans="3:15" hidden="1">
       <c r="C173" t="s">
         <v>521</v>
       </c>
@@ -11422,7 +11463,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" spans="3:15">
+    <row r="174" spans="3:15" hidden="1">
       <c r="C174" t="s">
         <v>524</v>
       </c>
@@ -11463,7 +11504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="3:15">
+    <row r="175" spans="3:15" hidden="1">
       <c r="C175" t="s">
         <v>524</v>
       </c>
@@ -11504,7 +11545,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="3:15">
+    <row r="176" spans="3:15" hidden="1">
       <c r="C176" t="s">
         <v>528</v>
       </c>
@@ -11545,7 +11586,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="177" spans="3:15">
+    <row r="177" spans="3:15" hidden="1">
       <c r="C177" t="s">
         <v>532</v>
       </c>
@@ -11586,7 +11627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="3:15">
+    <row r="178" spans="3:15" hidden="1">
       <c r="C178" t="s">
         <v>535</v>
       </c>
@@ -11627,7 +11668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="3:15">
+    <row r="179" spans="3:15" hidden="1">
       <c r="C179" t="s">
         <v>535</v>
       </c>
@@ -11668,7 +11709,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="3:15">
+    <row r="180" spans="3:15" hidden="1">
       <c r="C180" t="s">
         <v>538</v>
       </c>
@@ -11709,7 +11750,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="3:15">
+    <row r="181" spans="3:15" hidden="1">
       <c r="C181" t="s">
         <v>541</v>
       </c>
@@ -11750,7 +11791,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="3:15">
+    <row r="182" spans="3:15" hidden="1">
       <c r="C182" t="s">
         <v>542</v>
       </c>
@@ -11791,7 +11832,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="3:15">
+    <row r="183" spans="3:15" hidden="1">
       <c r="C183" t="s">
         <v>545</v>
       </c>
@@ -11832,7 +11873,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="3:15">
+    <row r="184" spans="3:15" hidden="1">
       <c r="C184" t="s">
         <v>548</v>
       </c>
@@ -11873,7 +11914,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="3:15">
+    <row r="185" spans="3:15" hidden="1">
       <c r="C185" t="s">
         <v>548</v>
       </c>
@@ -11914,7 +11955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="3:15">
+    <row r="186" spans="3:15" hidden="1">
       <c r="C186" t="s">
         <v>551</v>
       </c>
@@ -11955,7 +11996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="3:15">
+    <row r="187" spans="3:15" hidden="1">
       <c r="C187" t="s">
         <v>551</v>
       </c>
@@ -11996,7 +12037,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="3:15">
+    <row r="188" spans="3:15" hidden="1">
       <c r="C188" t="s">
         <v>556</v>
       </c>
@@ -12037,7 +12078,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="3:15">
+    <row r="189" spans="3:15" hidden="1">
       <c r="C189" t="s">
         <v>559</v>
       </c>
@@ -12078,7 +12119,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="3:15">
+    <row r="190" spans="3:15" hidden="1">
       <c r="C190" t="s">
         <v>562</v>
       </c>
@@ -12119,7 +12160,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="3:15">
+    <row r="191" spans="3:15" hidden="1">
       <c r="C191" t="s">
         <v>565</v>
       </c>
@@ -12160,7 +12201,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="3:15">
+    <row r="192" spans="3:15" hidden="1">
       <c r="C192" t="s">
         <v>568</v>
       </c>
@@ -12201,7 +12242,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="193" spans="3:15">
+    <row r="193" spans="3:15" hidden="1">
       <c r="C193" t="s">
         <v>571</v>
       </c>
@@ -12242,7 +12283,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="3:15">
+    <row r="194" spans="3:15" hidden="1">
       <c r="C194" t="s">
         <v>574</v>
       </c>
@@ -12283,7 +12324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="3:15">
+    <row r="195" spans="3:15" hidden="1">
       <c r="C195" t="s">
         <v>574</v>
       </c>
@@ -12324,7 +12365,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="3:15">
+    <row r="196" spans="3:15" hidden="1">
       <c r="C196" t="s">
         <v>576</v>
       </c>
@@ -12365,7 +12406,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="3:15">
+    <row r="197" spans="3:15" hidden="1">
       <c r="C197" t="s">
         <v>579</v>
       </c>
@@ -12406,7 +12447,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="3:15">
+    <row r="198" spans="3:15" hidden="1">
       <c r="C198" t="s">
         <v>582</v>
       </c>
@@ -12447,7 +12488,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="3:15">
+    <row r="199" spans="3:15" hidden="1">
       <c r="C199" t="s">
         <v>585</v>
       </c>
@@ -12488,7 +12529,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="3:15">
+    <row r="200" spans="3:15" hidden="1">
       <c r="C200" t="s">
         <v>588</v>
       </c>
@@ -12529,7 +12570,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="201" spans="3:15">
+    <row r="201" spans="3:15" hidden="1">
       <c r="C201" t="s">
         <v>591</v>
       </c>
@@ -12570,7 +12611,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="202" spans="3:15">
+    <row r="202" spans="3:15" hidden="1">
       <c r="C202" t="s">
         <v>594</v>
       </c>
@@ -12611,7 +12652,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="203" spans="3:15">
+    <row r="203" spans="3:15" hidden="1">
       <c r="C203" t="s">
         <v>596</v>
       </c>
@@ -12652,7 +12693,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="3:15">
+    <row r="204" spans="3:15" hidden="1">
       <c r="C204" t="s">
         <v>599</v>
       </c>
@@ -12693,7 +12734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="205" spans="3:15">
+    <row r="205" spans="3:15" hidden="1">
       <c r="C205" t="s">
         <v>602</v>
       </c>
@@ -12734,7 +12775,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="206" spans="3:15">
+    <row r="206" spans="3:15" hidden="1">
       <c r="C206" t="s">
         <v>602</v>
       </c>
@@ -12775,7 +12816,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="207" spans="3:15">
+    <row r="207" spans="3:15" hidden="1">
       <c r="C207" t="s">
         <v>605</v>
       </c>
@@ -12816,7 +12857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="3:15">
+    <row r="208" spans="3:15" hidden="1">
       <c r="C208" t="s">
         <v>608</v>
       </c>
@@ -12857,7 +12898,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="209" spans="3:15">
+    <row r="209" spans="3:15" hidden="1">
       <c r="C209" t="s">
         <v>611</v>
       </c>
@@ -12898,7 +12939,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="210" spans="3:15">
+    <row r="210" spans="3:15" hidden="1">
       <c r="C210" t="s">
         <v>614</v>
       </c>
@@ -12939,7 +12980,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="211" spans="3:15">
+    <row r="211" spans="3:15" hidden="1">
       <c r="C211" t="s">
         <v>617</v>
       </c>
@@ -12980,7 +13021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="212" spans="3:15">
+    <row r="212" spans="3:15" hidden="1">
       <c r="C212" t="s">
         <v>620</v>
       </c>
@@ -13021,7 +13062,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="213" spans="3:15">
+    <row r="213" spans="3:15" hidden="1">
       <c r="C213" t="s">
         <v>623</v>
       </c>
@@ -13062,7 +13103,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="214" spans="3:15">
+    <row r="214" spans="3:15" hidden="1">
       <c r="C214" t="s">
         <v>626</v>
       </c>
@@ -13103,7 +13144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="215" spans="3:15">
+    <row r="215" spans="3:15" hidden="1">
       <c r="C215" t="s">
         <v>629</v>
       </c>
@@ -13144,7 +13185,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" spans="3:15">
+    <row r="216" spans="3:15" hidden="1">
       <c r="C216" t="s">
         <v>629</v>
       </c>
@@ -13185,7 +13226,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="217" spans="3:15">
+    <row r="217" spans="3:15" hidden="1">
       <c r="C217" t="s">
         <v>634</v>
       </c>
@@ -13226,7 +13267,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="218" spans="3:15">
+    <row r="218" spans="3:15" hidden="1">
       <c r="C218" t="s">
         <v>637</v>
       </c>
@@ -13267,7 +13308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="219" spans="3:15">
+    <row r="219" spans="3:15" hidden="1">
       <c r="C219" t="s">
         <v>640</v>
       </c>
@@ -13308,7 +13349,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="220" spans="3:15">
+    <row r="220" spans="3:15" hidden="1">
       <c r="C220" t="s">
         <v>643</v>
       </c>
@@ -13349,7 +13390,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="221" spans="3:15">
+    <row r="221" spans="3:15" hidden="1">
       <c r="C221" t="s">
         <v>646</v>
       </c>
@@ -13390,7 +13431,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="3:15">
+    <row r="222" spans="3:15" hidden="1">
       <c r="C222" t="s">
         <v>649</v>
       </c>
@@ -13431,7 +13472,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="3:15">
+    <row r="223" spans="3:15" hidden="1">
       <c r="C223" t="s">
         <v>649</v>
       </c>
@@ -13472,7 +13513,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" spans="3:15">
+    <row r="224" spans="3:15" hidden="1">
       <c r="C224" t="s">
         <v>652</v>
       </c>
@@ -13513,7 +13554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="225" spans="3:15">
+    <row r="225" spans="3:15" hidden="1">
       <c r="C225" t="s">
         <v>655</v>
       </c>
@@ -13554,7 +13595,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="226" spans="3:15">
+    <row r="226" spans="3:15" hidden="1">
       <c r="C226" t="s">
         <v>658</v>
       </c>
@@ -13595,7 +13636,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="227" spans="3:15">
+    <row r="227" spans="3:15" hidden="1">
       <c r="C227" t="s">
         <v>662</v>
       </c>
@@ -13636,7 +13677,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="3:15">
+    <row r="228" spans="3:15" hidden="1">
       <c r="C228" t="s">
         <v>662</v>
       </c>
@@ -13677,7 +13718,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="3:15">
+    <row r="229" spans="3:15" hidden="1">
       <c r="C229" t="s">
         <v>665</v>
       </c>
@@ -13718,7 +13759,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="3:15">
+    <row r="230" spans="3:15" hidden="1">
       <c r="C230" t="s">
         <v>668</v>
       </c>
@@ -13759,7 +13800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="3:15">
+    <row r="231" spans="3:15" hidden="1">
       <c r="C231" t="s">
         <v>668</v>
       </c>
@@ -13800,7 +13841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="3:15">
+    <row r="232" spans="3:15" hidden="1">
       <c r="C232" t="s">
         <v>671</v>
       </c>
@@ -13841,7 +13882,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="233" spans="3:15">
+    <row r="233" spans="3:15" hidden="1">
       <c r="C233" t="s">
         <v>674</v>
       </c>
@@ -13882,7 +13923,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="234" spans="3:15">
+    <row r="234" spans="3:15" hidden="1">
       <c r="C234" t="s">
         <v>677</v>
       </c>
@@ -13923,7 +13964,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="235" spans="3:15">
+    <row r="235" spans="3:15" hidden="1">
       <c r="C235" t="s">
         <v>680</v>
       </c>
@@ -13964,7 +14005,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="236" spans="3:15">
+    <row r="236" spans="3:15" hidden="1">
       <c r="C236" t="s">
         <v>683</v>
       </c>
@@ -14005,7 +14046,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="237" spans="3:15">
+    <row r="237" spans="3:15" hidden="1">
       <c r="C237" t="s">
         <v>686</v>
       </c>
@@ -14046,7 +14087,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="3:15">
+    <row r="238" spans="3:15" hidden="1">
       <c r="C238" t="s">
         <v>689</v>
       </c>
@@ -14087,7 +14128,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="239" spans="3:15">
+    <row r="239" spans="3:15" hidden="1">
       <c r="C239" t="s">
         <v>692</v>
       </c>
@@ -14128,7 +14169,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="3:15">
+    <row r="240" spans="3:15" hidden="1">
       <c r="C240" t="s">
         <v>695</v>
       </c>
@@ -14169,7 +14210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="3:15">
+    <row r="241" spans="3:15" hidden="1">
       <c r="C241" t="s">
         <v>695</v>
       </c>
@@ -14210,7 +14251,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="3:15">
+    <row r="242" spans="3:15" hidden="1">
       <c r="C242" t="s">
         <v>698</v>
       </c>
@@ -14251,7 +14292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="243" spans="3:15">
+    <row r="243" spans="3:15" hidden="1">
       <c r="C243" t="s">
         <v>701</v>
       </c>
@@ -14292,7 +14333,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="244" spans="3:15">
+    <row r="244" spans="3:15" hidden="1">
       <c r="C244" t="s">
         <v>701</v>
       </c>
@@ -14333,7 +14374,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="245" spans="3:15">
+    <row r="245" spans="3:15" hidden="1">
       <c r="C245" t="s">
         <v>704</v>
       </c>
@@ -14374,7 +14415,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="246" spans="3:15">
+    <row r="246" spans="3:15" hidden="1">
       <c r="C246" t="s">
         <v>707</v>
       </c>
@@ -14415,7 +14456,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="247" spans="3:15">
+    <row r="247" spans="3:15" hidden="1">
       <c r="C247" t="s">
         <v>710</v>
       </c>
@@ -14456,7 +14497,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="248" spans="3:15">
+    <row r="248" spans="3:15" hidden="1">
       <c r="C248" t="s">
         <v>713</v>
       </c>
@@ -14497,7 +14538,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="249" spans="3:15">
+    <row r="249" spans="3:15" hidden="1">
       <c r="C249" t="s">
         <v>716</v>
       </c>
@@ -14538,7 +14579,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="250" spans="3:15">
+    <row r="250" spans="3:15" hidden="1">
       <c r="C250" t="s">
         <v>719</v>
       </c>
@@ -14579,7 +14620,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="251" spans="3:15">
+    <row r="251" spans="3:15" hidden="1">
       <c r="C251" t="s">
         <v>722</v>
       </c>
@@ -14620,7 +14661,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="252" spans="3:15">
+    <row r="252" spans="3:15" hidden="1">
       <c r="C252" t="s">
         <v>725</v>
       </c>
@@ -14661,7 +14702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="3:15">
+    <row r="253" spans="3:15" hidden="1">
       <c r="C253" t="s">
         <v>725</v>
       </c>
@@ -14702,7 +14743,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="254" spans="3:15">
+    <row r="254" spans="3:15" hidden="1">
       <c r="C254" t="s">
         <v>728</v>
       </c>
@@ -14743,7 +14784,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="255" spans="3:15">
+    <row r="255" spans="3:15" hidden="1">
       <c r="C255" t="s">
         <v>728</v>
       </c>
@@ -14784,7 +14825,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="256" spans="3:15">
+    <row r="256" spans="3:15" hidden="1">
       <c r="C256" t="s">
         <v>733</v>
       </c>
@@ -14825,7 +14866,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="257" spans="3:15">
+    <row r="257" spans="3:15" hidden="1">
       <c r="C257" t="s">
         <v>736</v>
       </c>
@@ -14866,7 +14907,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="258" spans="3:15">
+    <row r="258" spans="3:15" hidden="1">
       <c r="C258" t="s">
         <v>739</v>
       </c>
@@ -14907,7 +14948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="259" spans="3:15">
+    <row r="259" spans="3:15" hidden="1">
       <c r="C259" t="s">
         <v>739</v>
       </c>
@@ -14948,7 +14989,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="260" spans="3:15">
+    <row r="260" spans="3:15" hidden="1">
       <c r="C260" t="s">
         <v>744</v>
       </c>
@@ -14989,7 +15030,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="261" spans="3:15">
+    <row r="261" spans="3:15" hidden="1">
       <c r="C261" t="s">
         <v>747</v>
       </c>
@@ -15030,7 +15071,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="262" spans="3:15">
+    <row r="262" spans="3:15" hidden="1">
       <c r="C262" t="s">
         <v>750</v>
       </c>
@@ -15071,7 +15112,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="263" spans="3:15">
+    <row r="263" spans="3:15" hidden="1">
       <c r="C263" t="s">
         <v>753</v>
       </c>
@@ -15112,7 +15153,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="264" spans="3:15">
+    <row r="264" spans="3:15" hidden="1">
       <c r="C264" t="s">
         <v>756</v>
       </c>
@@ -15153,7 +15194,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="265" spans="3:15">
+    <row r="265" spans="3:15" hidden="1">
       <c r="C265" t="s">
         <v>759</v>
       </c>
@@ -15194,7 +15235,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="266" spans="3:15">
+    <row r="266" spans="3:15" hidden="1">
       <c r="C266" t="s">
         <v>762</v>
       </c>
@@ -15235,7 +15276,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="267" spans="3:15">
+    <row r="267" spans="3:15" hidden="1">
       <c r="C267" t="s">
         <v>765</v>
       </c>
@@ -18941,4 +18982,455 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056D4C31-6BF7-4F39-B5EE-B0BC201D12D6}">
+  <dimension ref="A4:C22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:3">
+      <c r="B4" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="str">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A6,FALSE),"Not Found")</f>
+        <v>Edd</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="str">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A7,FALSE),"Not Found")</f>
+        <v>MacKnockiter</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="str">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A8,FALSE),"Not Found")</f>
+        <v>Accounting</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <f>IFERROR(VLOOKUP($C$4,staff[],A9,FALSE),"Not Found")</f>
+        <v>119022.49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="C18">
+        <f>MATCH(C17,staff[Last Name],0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="34" t="s">
+        <v>780</v>
+      </c>
+      <c r="C20" t="str">
+        <f>INDEX(staff[Emp ID],MATCH(C17,staff[Last Name],0))</f>
+        <v>PR00113</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="str">
+        <f>INDEX(staff[Department],MATCH(C17,staff[Last Name],0))</f>
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22">
+        <f>INDEX(staff[Salary],MATCH(C17,staff[Last Name],0))</f>
+        <v>80695.740000000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46536243-F308-454E-A744-58FF22B55FB4}">
+  <dimension ref="B4:N44"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:3">
+      <c r="B4" s="28" t="s">
+        <v>781</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" t="s">
+        <v>782</v>
+      </c>
+      <c r="C6" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[First Name],"Not Found")</f>
+        <v>Edd</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>783</v>
+      </c>
+      <c r="C7" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Last Name],"Not Found")</f>
+        <v>MacKnockiter</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Department],"Not Found")</f>
+        <v>Accounting</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Salary],"Not Found")</f>
+        <v>119022.49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" s="28" t="s">
+        <v>783</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="34" t="s">
+        <v>781</v>
+      </c>
+      <c r="C17" t="str">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Emp ID],"Not Found")</f>
+        <v>PR00113</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="str">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Department],"Not Found")</f>
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Salary],"Not Found")</f>
+        <v>80695.740000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="34" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" t="str" cm="1">
+        <f t="array" ref="B23:N23">_xlfn.XLOOKUP(C14,staff[Last Name],staff[],"Not Found")</f>
+        <v>PR00113</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G23">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H23" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I23">
+        <v>43360</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M23">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="34" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" t="str" cm="1">
+        <f t="array" ref="B26:B38">TRANSPOSE(_xlfn.XLOOKUP(C14,staff[Last Name],staff[],"Not Found"))</f>
+        <v>PR00113</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" t="str">
+        <v>Van</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" t="str">
+        <v>Tuxwell</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" t="str">
+        <v>Female</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" t="str">
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31">
+        <v>80695.740000000005</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" t="str">
+        <v>50k to 100k</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33">
+        <v>43360</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" t="str">
+        <v>Permanent</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" t="str">
+        <v>Columbus, USA</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
+      <c r="B37">
+        <v>5.7643835616438359</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
+      <c r="B38" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" ht="30.75">
+      <c r="B41" s="36" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
+      <c r="B42" t="str" cm="1">
+        <f t="array" ref="B42:N44">_xlfn._xlws.FILTER(staff[], staff[Last Name]=C14)</f>
+        <v>PR00113</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G42">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H42" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I42">
+        <v>43360</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M42">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
+      <c r="B43" t="str">
+        <v>PR00113</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G43">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H43" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I43">
+        <v>43360</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M43">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
+      <c r="B44" t="str">
+        <v>PR04380</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Van</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G44">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H44" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I44">
+        <v>43787</v>
+      </c>
+      <c r="J44">
+        <v>0.8</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M44">
+        <v>4.5945205479452058</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel/PracticeExcel/02Functions_Formulas/sample-data-fx.blank.xlsx
+++ b/Excel/PracticeExcel/02Functions_Formulas/sample-data-fx.blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Documents\PythonClassSF\DataAnalytics01\Excel\02Functions_Formulas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F724FB2C-EACB-470B-9067-2343E8D16EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF15CC53-F4AD-4AEC-823D-00FE6B5EEA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="9" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Task 05" sheetId="7" r:id="rId7"/>
     <sheet name="Task 06" sheetId="8" r:id="rId8"/>
     <sheet name="Task 07" sheetId="9" r:id="rId9"/>
+    <sheet name="Task 08" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="791">
   <si>
     <t>Essential Excel Functions &amp; Formulas</t>
   </si>
@@ -2427,6 +2428,18 @@
   </si>
   <si>
     <t>Entire All Data Get by last name using Filter</t>
+  </si>
+  <si>
+    <t>Max Salary</t>
+  </si>
+  <si>
+    <t>One Person</t>
+  </si>
+  <si>
+    <t>All Persons</t>
+  </si>
+  <si>
+    <t>All Persons in one cell</t>
   </si>
 </sst>
 </file>
@@ -2583,7 +2596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2665,6 +2678,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4589,6 +4605,61 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA0DA60-8DD2-4304-9D73-1D30DBAF95DD}">
+  <dimension ref="B3:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="47.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3">
+      <c r="B3" s="28" t="s">
+        <v>787</v>
+      </c>
+      <c r="C3">
+        <f>MAX(staff[Salary])</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B6" s="28" t="s">
+        <v>788</v>
+      </c>
+      <c r="C6" s="31" t="str" cm="1">
+        <f t="array" ref="C6">_xlfn.XLOOKUP(MAX(staff[Salary]), staff[Salary], staff[First Name]&amp;" "&amp;staff[Last Name])</f>
+        <v>Minerva Ricardot</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" s="28" t="s">
+        <v>789</v>
+      </c>
+      <c r="C10" t="str" cm="1">
+        <f t="array" ref="C10:C11">_xlfn._xlws.FILTER(staff[First Name]&amp;" "&amp;staff[Last Name], staff[Salary]=MAX(staff[Salary]))</f>
+        <v>Minerva Ricardot</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="C11" t="str">
+        <v>Mick Spraberry</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="30.75">
+      <c r="B14" s="37" t="s">
+        <v>790</v>
+      </c>
+      <c r="C14" s="31" t="str" cm="1">
+        <f t="array" ref="C14">_xlfn.TEXTJOIN(",",,_xlfn._xlws.FILTER(staff[First Name]&amp;" "&amp;staff[Last Name], staff[Salary]=MAX(staff[Salary])))</f>
+        <v>Minerva Ricardot,Mick Spraberry</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE182796-6443-4558-9B87-909B73329DFC}">
   <dimension ref="A1:O267"/>

--- a/Excel/PracticeExcel/02Functions_Formulas/sample-data-fx.blank.xlsx
+++ b/Excel/PracticeExcel/02Functions_Formulas/sample-data-fx.blank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Documents\PythonClassSF\DataAnalytics01\Excel\02Functions_Formulas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF15CC53-F4AD-4AEC-823D-00FE6B5EEA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{424EE42B-32EC-44D0-85F2-C9B2415AC001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="9" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="11" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="Task 06" sheetId="8" r:id="rId8"/>
     <sheet name="Task 07" sheetId="9" r:id="rId9"/>
     <sheet name="Task 08" sheetId="10" r:id="rId10"/>
+    <sheet name="Task 09" sheetId="11" r:id="rId11"/>
+    <sheet name="Task 10" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -67,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="797">
   <si>
     <t>Essential Excel Functions &amp; Formulas</t>
   </si>
@@ -2440,18 +2442,37 @@
   </si>
   <si>
     <t>All Persons in one cell</t>
+  </si>
+  <si>
+    <t>All Departments</t>
+  </si>
+  <si>
+    <t>Avg. Salary</t>
+  </si>
+  <si>
+    <t>% diff from overall avg</t>
+  </si>
+  <si>
+    <t>Median Salary</t>
+  </si>
+  <si>
+    <t>Female Ratio</t>
+  </si>
+  <si>
+    <t>Total Count Female</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2501,8 +2522,23 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2542,6 +2578,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2596,7 +2638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2683,6 +2725,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2814,13 +2863,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}" name="staff" displayName="staff" ref="C7:O267" totalsRowShown="0">
-  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Tuxwell"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:O267">
     <sortCondition ref="C7:C267"/>
   </sortState>
@@ -4660,6 +4703,5243 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE30797-3B4B-4C30-8236-A3EC81863B5B}">
+  <dimension ref="B3:N136"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:14">
+      <c r="B3" s="38" t="str" cm="1">
+        <f t="array" ref="B3:N3">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C3" s="38" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E3" s="38" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F3" s="38" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G3" s="38" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H3" s="38" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I3" s="38" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J3" s="38" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K3" s="38" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L3" s="38" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M3" s="38" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N3" s="38" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" t="str" cm="1">
+        <f t="array" ref="B4:N10">_xlfn._xlws.FILTER(staff[], LEFT(staff[First Name],1)="H")</f>
+        <v>PR00246</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Husein</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Augar</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G4">
+        <v>67905.8</v>
+      </c>
+      <c r="H4" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I4">
+        <v>44194</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M4">
+        <v>3.4794520547945207</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" t="str">
+        <v>PR00746</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G5">
+        <v>114177.23</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I5">
+        <v>43908</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M5">
+        <v>4.2630136986301368</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" t="str">
+        <v>SQ04437</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Hephzibah</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Summerell</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G6">
+        <v>28305.08</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I6">
+        <v>43754</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M6">
+        <v>4.6849315068493151</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" t="str">
+        <v>TN00214</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Hemavati</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Muthiah</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G7">
+        <v>37902.35</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I7">
+        <v>43823</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M7">
+        <v>4.4958904109589044</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" t="str">
+        <v>TN04175</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Hinda</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Label</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G8">
+        <v>92704.48</v>
+      </c>
+      <c r="H8" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I8">
+        <v>43430</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M8">
+        <v>5.5726027397260278</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" t="str">
+        <v>TN04775</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Hridaynath</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Tendulkar</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G9">
+        <v>31089.22</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I9">
+        <v>43776</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M9">
+        <v>4.624657534246575</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" t="str">
+        <v>VT01996</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Hali</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Behnecke</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G10">
+        <v>65569.36</v>
+      </c>
+      <c r="H10" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I10">
+        <v>43293</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M10">
+        <v>5.9479452054794519</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="28" t="str" cm="1">
+        <f t="array" ref="B13:N13">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C13" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D13" s="28" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E13" s="28" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F13" s="28" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G13" s="28" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H13" s="28" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I13" s="28" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J13" s="28" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K13" s="28" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L13" s="28" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M13" s="28" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N13" s="28" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" t="str" cm="1">
+        <f t="array" ref="B14:N58">_xlfn._xlws.FILTER(staff[],staff[Start Date]&gt;=DATE(2021,1,1))</f>
+        <v>PR00882</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Jill</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Shipsey</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G14">
+        <v>52963.65</v>
+      </c>
+      <c r="H14" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I14" s="30">
+        <v>44288</v>
+      </c>
+      <c r="J14">
+        <v>0.3</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M14">
+        <v>3.2219178082191782</v>
+      </c>
+      <c r="N14" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Veeravasarapu</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G15">
+        <v>50310.09</v>
+      </c>
+      <c r="H15" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I15" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J15">
+        <v>0.4</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M15">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16" t="str">
+        <v>PR00916</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Inger</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Chapelhow</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G16">
+        <v>84309.95</v>
+      </c>
+      <c r="H16" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I16" s="30">
+        <v>44501</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M16">
+        <v>2.6383561643835618</v>
+      </c>
+      <c r="N16" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" t="str">
+        <v>PR01211</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Enoch</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Dowrey</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G17">
+        <v>91645.04</v>
+      </c>
+      <c r="H17" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I17" s="30">
+        <v>44223</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M17">
+        <v>3.4</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" t="str">
+        <v>PR01269</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Eleonore</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Airdrie</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G18">
+        <v>97105.19</v>
+      </c>
+      <c r="H18" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I18" s="30">
+        <v>44425</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M18">
+        <v>2.8465753424657536</v>
+      </c>
+      <c r="N18" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" t="str">
+        <v>PR01383</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Addi</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Studdeard</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G19">
+        <v>72502.61</v>
+      </c>
+      <c r="H19" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I19" s="30">
+        <v>44235</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M19">
+        <v>3.3671232876712329</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" t="str">
+        <v>PR02208</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Gowri</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Sankar</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G20">
+        <v>102934.09</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I20" s="30">
+        <v>44315</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M20">
+        <v>3.1479452054794521</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" t="str">
+        <v>PR03034</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Sreenivasa</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Naik</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G21">
+        <v>32192.15</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I21" s="30">
+        <v>44473</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M21">
+        <v>2.7150684931506848</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" t="str">
+        <v>PR03445</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Myrle</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Prandoni</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G22">
+        <v>62195.47</v>
+      </c>
+      <c r="H22" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I22" s="30">
+        <v>44434</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M22">
+        <v>2.8219178082191783</v>
+      </c>
+      <c r="N22" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" t="str">
+        <v>PR03886</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Edd</v>
+      </c>
+      <c r="D23" t="str">
+        <v>MacKnockiter</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G23">
+        <v>119022.49</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I23" s="30">
+        <v>44431</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M23">
+        <v>2.8301369863013699</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" t="str">
+        <v>PR04446</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Sameer</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Shashank</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G24">
+        <v>92336.08</v>
+      </c>
+      <c r="H24" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I24" s="30">
+        <v>44431</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M24">
+        <v>2.8301369863013699</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" t="str">
+        <v>PR04473</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Wyn</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Treadger</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G25">
+        <v>69192.850000000006</v>
+      </c>
+      <c r="H25" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I25" s="30">
+        <v>44305</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M25">
+        <v>3.1753424657534248</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" t="str">
+        <v>PR04601</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Yedukondalu</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Panditula</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Need to check</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Support</v>
+      </c>
+      <c r="G26">
+        <v>104802.63</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I26" s="30">
+        <v>44502</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M26">
+        <v>2.6356164383561644</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" t="str">
+        <v>SQ00286</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Ilesh</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Dasgupta</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G27">
+        <v>61213.01</v>
+      </c>
+      <c r="H27" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I27" s="30">
+        <v>44365</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M27">
+        <v>3.010958904109589</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" t="str">
+        <v>SQ00498</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Amery</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Ofer</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G28">
+        <v>111049.84</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I28" s="30">
+        <v>44393</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M28">
+        <v>2.9342465753424656</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" t="str">
+        <v>SQ01026</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Anumati</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Shyamari</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G29">
+        <v>74924.649999999994</v>
+      </c>
+      <c r="H29" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I29" s="30">
+        <v>44239</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M29">
+        <v>3.3561643835616439</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" t="str">
+        <v>SQ01395</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Dennison</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Crosswaite</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G30">
+        <v>90697.67</v>
+      </c>
+      <c r="H30" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I30" s="30">
+        <v>44221</v>
+      </c>
+      <c r="J30">
+        <v>0.8</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="M30">
+        <v>3.4054794520547946</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" t="str">
+        <v>SQ01998</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Vanmala</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Shriharsha</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G31">
+        <v>40445.29</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I31" s="30">
+        <v>44393</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M31">
+        <v>2.9342465753424656</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" t="str">
+        <v>SQ01998</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Sahas</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Sanabhi</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G32">
+        <v>40445.29</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I32" s="30">
+        <v>44393</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M32">
+        <v>2.9342465753424656</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33" t="str">
+        <v>SQ02525</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Mickie</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Dagwell</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G33">
+        <v>50855.53</v>
+      </c>
+      <c r="H33" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I33" s="30">
+        <v>44221</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M33">
+        <v>3.4054794520547946</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" t="str">
+        <v>SQ02565</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Konstantin</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Timblett</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G34">
+        <v>56253.81</v>
+      </c>
+      <c r="H34" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I34" s="30">
+        <v>44421</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M34">
+        <v>2.8575342465753426</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" t="str">
+        <v>SQ02624</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Gwenneth</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Fealey</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G35">
+        <v>114772.32</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I35" s="30">
+        <v>44251</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M35">
+        <v>3.3232876712328765</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" t="str">
+        <v>SQ03491</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Freda</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Legan</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G36">
+        <v>102129.37</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I36" s="30">
+        <v>44396</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M36">
+        <v>2.9260273972602739</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
+      <c r="B37" t="str">
+        <v>SQ03546</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Amlankusum</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Rajabhushan</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G37">
+        <v>75733.740000000005</v>
+      </c>
+      <c r="H37" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I37" s="30">
+        <v>44382</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M37">
+        <v>2.9643835616438357</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
+      <c r="B38" t="str">
+        <v>SQ03626</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Krishnakanta</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Vellanki</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G38">
+        <v>95677.9</v>
+      </c>
+      <c r="H38" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I38" s="30">
+        <v>44396</v>
+      </c>
+      <c r="J38">
+        <v>0.3</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M38">
+        <v>2.9260273972602739</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
+      <c r="B39" t="str">
+        <v>TN00890</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Mayur</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Kousika</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G39">
+        <v>71570.990000000005</v>
+      </c>
+      <c r="H39" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I39" s="30">
+        <v>44249</v>
+      </c>
+      <c r="J39">
+        <v>0.5</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M39">
+        <v>3.3287671232876712</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
+      <c r="B40" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G40">
+        <v>68795.48</v>
+      </c>
+      <c r="H40" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I40" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J40">
+        <v>0.2</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M40">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
+      <c r="B41" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G41">
+        <v>68795.48</v>
+      </c>
+      <c r="H41" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I41" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J41">
+        <v>0.2</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M41">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
+      <c r="B42" t="str">
+        <v>TN02674</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Antonetta</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Coggeshall</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G42">
+        <v>96753.78</v>
+      </c>
+      <c r="H42" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I42" s="30">
+        <v>44494</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M42">
+        <v>2.6575342465753424</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
+      <c r="B43" t="str">
+        <v>TN02674</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Antonetta</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Coggeshall</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G43">
+        <v>96753.78</v>
+      </c>
+      <c r="H43" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I43" s="30">
+        <v>44494</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M43">
+        <v>2.6575342465753424</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
+      <c r="B44" t="str">
+        <v>TN02988</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Mahindra</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Sreedharan</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G44">
+        <v>92943.89</v>
+      </c>
+      <c r="H44" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I44" s="30">
+        <v>44510</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M44">
+        <v>2.6136986301369864</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
+      <c r="B45" t="str">
+        <v>TN03032</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Jaipal</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Potanapudi</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G45">
+        <v>39700.82</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I45" s="30">
+        <v>44203</v>
+      </c>
+      <c r="J45">
+        <v>0.8</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M45">
+        <v>3.4547945205479453</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
+      <c r="B46" t="str">
+        <v>TN03032</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Fullara</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Sushanti</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="G46">
+        <v>39700.82</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I46" s="30">
+        <v>44203</v>
+      </c>
+      <c r="J46">
+        <v>0.8</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M46">
+        <v>3.4547945205479453</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
+      <c r="B47" t="str">
+        <v>TN04265</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Rushil</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Kripa</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G47">
+        <v>93964.3</v>
+      </c>
+      <c r="H47" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I47" s="30">
+        <v>44454</v>
+      </c>
+      <c r="J47">
+        <v>0.4</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M47">
+        <v>2.7671232876712328</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
+      <c r="B48" t="str">
+        <v>VT00194</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Violante</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Courtonne</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G48">
+        <v>49625.64</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I48" s="30">
+        <v>44384</v>
+      </c>
+      <c r="J48">
+        <v>0.5</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M48">
+        <v>2.9589041095890409</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14">
+      <c r="B49" t="str">
+        <v>VT00578</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Magnum</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Locksley</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G49">
+        <v>42314.39</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I49" s="30">
+        <v>44487</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M49">
+        <v>2.6767123287671235</v>
+      </c>
+      <c r="N49" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14">
+      <c r="B50" t="str">
+        <v>VT01249</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Brendan</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Edgeller</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G50">
+        <v>31042.51</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I50" s="30">
+        <v>44473</v>
+      </c>
+      <c r="J50">
+        <v>0.3</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M50">
+        <v>2.7150684931506848</v>
+      </c>
+      <c r="N50" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14">
+      <c r="B51" t="str">
+        <v>VT02118</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Oorjit</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Nandanavanam</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G51">
+        <v>51165.37</v>
+      </c>
+      <c r="H51" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I51" s="30">
+        <v>44237</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M51">
+        <v>3.3616438356164382</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14">
+      <c r="B52" t="str">
+        <v>VT02663</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Sravanthi</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Chalaki</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G52">
+        <v>28481.16</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I52" s="30">
+        <v>44228</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M52">
+        <v>3.3863013698630136</v>
+      </c>
+      <c r="N52" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14">
+      <c r="B53" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G53">
+        <v>113747.56</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I53" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J53">
+        <v>0.7</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M53">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N53" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14">
+      <c r="B54" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G54">
+        <v>113747.56</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I54" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J54">
+        <v>0.7</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M54">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N54" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14">
+      <c r="B55" t="str">
+        <v>VT03500</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Shiuli</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Sapna</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Support</v>
+      </c>
+      <c r="G55">
+        <v>37062.1</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I55" s="30">
+        <v>44357</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M55">
+        <v>3.032876712328767</v>
+      </c>
+      <c r="N55" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14">
+      <c r="B56" t="str">
+        <v>VT03552</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Kamalakshi</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Mukundan</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G56">
+        <v>36536.26</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I56" s="30">
+        <v>44358</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M56">
+        <v>3.0301369863013701</v>
+      </c>
+      <c r="N56" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14">
+      <c r="B57" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Colbeck</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G57">
+        <v>83396.5</v>
+      </c>
+      <c r="H57" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I57" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M57">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N57" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14">
+      <c r="B58" t="str">
+        <v>VT04627</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Yvette</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Bett</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G58">
+        <v>76320.44</v>
+      </c>
+      <c r="H58" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I58" s="30">
+        <v>44383</v>
+      </c>
+      <c r="J58">
+        <v>0.8</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M58">
+        <v>2.9616438356164383</v>
+      </c>
+      <c r="N58" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14">
+      <c r="I59" s="30"/>
+    </row>
+    <row r="60" spans="2:14">
+      <c r="I60" s="30"/>
+    </row>
+    <row r="61" spans="2:14">
+      <c r="I61" s="30"/>
+    </row>
+    <row r="62" spans="2:14">
+      <c r="B62" s="28" t="str" cm="1">
+        <f t="array" ref="B62:N62">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C62" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D62" s="28" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E62" s="28" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F62" s="28" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G62" s="28" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H62" s="28" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I62" s="39" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J62" s="28" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K62" s="28" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L62" s="28" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M62" s="28" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N62" s="28" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14">
+      <c r="B63" t="str" cm="1">
+        <f t="array" ref="B63:N84">_xlfn._xlws.FILTER(staff[],MONTH(staff[Start Date])=3)</f>
+        <v>PR00746</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G63">
+        <v>114177.23</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I63" s="30">
+        <v>43908</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M63">
+        <v>4.2630136986301368</v>
+      </c>
+      <c r="N63" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14">
+      <c r="B64" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Veeravasarapu</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G64">
+        <v>50310.09</v>
+      </c>
+      <c r="H64" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I64" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J64">
+        <v>0.4</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M64">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N64" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14">
+      <c r="B65" t="str">
+        <v>SQ00022</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Carlin</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Demke</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="G65">
+        <v>110042.37</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I65" s="30">
+        <v>43914</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M65">
+        <v>4.2465753424657535</v>
+      </c>
+      <c r="N65" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14">
+      <c r="B66" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Ragunathan</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G66">
+        <v>86010.54</v>
+      </c>
+      <c r="H66" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I66" s="30">
+        <v>43164</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M66">
+        <v>6.3013698630136989</v>
+      </c>
+      <c r="N66" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
+      <c r="B67" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Kolakovic</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G67">
+        <v>49915.14</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I67" s="30">
+        <v>43550</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M67">
+        <v>5.2438356164383562</v>
+      </c>
+      <c r="N67" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14">
+      <c r="B68" t="str">
+        <v>SQ03112</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Kantimoy</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Pritish</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G68">
+        <v>77743.149999999994</v>
+      </c>
+      <c r="H68" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I68" s="30">
+        <v>43920</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M68">
+        <v>4.2301369863013702</v>
+      </c>
+      <c r="N68" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14">
+      <c r="B69" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Artis</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="G69">
+        <v>78020.39</v>
+      </c>
+      <c r="H69" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I69" s="30">
+        <v>43899</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M69">
+        <v>4.2876712328767121</v>
+      </c>
+      <c r="N69" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14">
+      <c r="B70" t="str">
+        <v>SQ04612</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Spraberry</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G70">
+        <v>120000</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I70" s="30">
+        <v>43902</v>
+      </c>
+      <c r="J70">
+        <v>0.9</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M70">
+        <v>4.279452054794521</v>
+      </c>
+      <c r="N70" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14">
+      <c r="B71" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Shattesh</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Utpat</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G71">
+        <v>28481.16</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I71" s="30">
+        <v>43916</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M71">
+        <v>4.2410958904109588</v>
+      </c>
+      <c r="N71" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14">
+      <c r="B72" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Sawini</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Chandan</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G72">
+        <v>28481.16</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I72" s="30">
+        <v>43916</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M72">
+        <v>4.2410958904109588</v>
+      </c>
+      <c r="N72" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14">
+      <c r="B73" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G73">
+        <v>68795.48</v>
+      </c>
+      <c r="H73" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I73" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J73">
+        <v>0.2</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M73">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N73" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
+      <c r="B74" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="G74">
+        <v>68795.48</v>
+      </c>
+      <c r="H74" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I74" s="30">
+        <v>44277</v>
+      </c>
+      <c r="J74">
+        <v>0.2</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M74">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="N74" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14">
+      <c r="B75" t="str">
+        <v>TN04892</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Wolstenholme</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G75">
+        <v>53184.02</v>
+      </c>
+      <c r="H75" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I75" s="30">
+        <v>43180</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M75">
+        <v>6.2575342465753421</v>
+      </c>
+      <c r="N75" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
+      <c r="B76" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Raghavanpillai</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G76">
+        <v>102515.81</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I76" s="30">
+        <v>43902</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M76">
+        <v>4.279452054794521</v>
+      </c>
+      <c r="N76" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
+      <c r="B77" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Linford</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G77">
+        <v>93128.34</v>
+      </c>
+      <c r="H77" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I77" s="30">
+        <v>43164</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="M77">
+        <v>6.3013698630136989</v>
+      </c>
+      <c r="N77" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14">
+      <c r="B78" t="str">
+        <v>VT02417</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Evangelina</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Lergan</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Support</v>
+      </c>
+      <c r="G78">
+        <v>61214.26</v>
+      </c>
+      <c r="H78" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I78" s="30">
+        <v>43171</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M78">
+        <v>6.2821917808219174</v>
+      </c>
+      <c r="N78" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
+      <c r="B79" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G79">
+        <v>113747.56</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I79" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J79">
+        <v>0.7</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M79">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N79" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14">
+      <c r="B80" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G80">
+        <v>113747.56</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I80" s="30">
+        <v>44270</v>
+      </c>
+      <c r="J80">
+        <v>0.7</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M80">
+        <v>3.2712328767123289</v>
+      </c>
+      <c r="N80" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14">
+      <c r="B81" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Colbeck</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G81">
+        <v>83396.5</v>
+      </c>
+      <c r="H81" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I81" s="30">
+        <v>44285</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M81">
+        <v>3.2301369863013698</v>
+      </c>
+      <c r="N81" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14">
+      <c r="B82" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G82">
+        <v>111815.49</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I82" s="30">
+        <v>43895</v>
+      </c>
+      <c r="J82">
+        <v>0.7</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M82">
+        <v>4.2986301369863016</v>
+      </c>
+      <c r="N82" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14">
+      <c r="B83" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G83">
+        <v>111815.49</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I83" s="30">
+        <v>43895</v>
+      </c>
+      <c r="J83">
+        <v>0.7</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M83">
+        <v>4.2986301369863016</v>
+      </c>
+      <c r="N83" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14">
+      <c r="B84" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Biles</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G84">
+        <v>58744.17</v>
+      </c>
+      <c r="H84" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I84" s="30">
+        <v>43171</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M84">
+        <v>6.2821917808219174</v>
+      </c>
+      <c r="N84" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14">
+      <c r="I85" s="30"/>
+    </row>
+    <row r="86" spans="2:14">
+      <c r="I86" s="30"/>
+    </row>
+    <row r="87" spans="2:14">
+      <c r="I87" s="30"/>
+    </row>
+    <row r="88" spans="2:14">
+      <c r="B88" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="I88" s="30"/>
+    </row>
+    <row r="89" spans="2:14">
+      <c r="B89" t="str" cm="1">
+        <f t="array" ref="B89:D110">_xlfn._xlws.FILTER(staff[[Emp ID]:[Last Name]],MONTH(staff[Start Date])=3)</f>
+        <v>PR00746</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="I89" s="30"/>
+    </row>
+    <row r="90" spans="2:14">
+      <c r="B90" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Veeravasarapu</v>
+      </c>
+      <c r="I90" s="30"/>
+    </row>
+    <row r="91" spans="2:14">
+      <c r="B91" t="str">
+        <v>SQ00022</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Carlin</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Demke</v>
+      </c>
+      <c r="I91" s="30"/>
+    </row>
+    <row r="92" spans="2:14">
+      <c r="B92" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Ragunathan</v>
+      </c>
+      <c r="I92" s="30"/>
+    </row>
+    <row r="93" spans="2:14">
+      <c r="B93" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Kolakovic</v>
+      </c>
+      <c r="I93" s="30"/>
+    </row>
+    <row r="94" spans="2:14">
+      <c r="B94" t="str">
+        <v>SQ03112</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Kantimoy</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Pritish</v>
+      </c>
+      <c r="I94" s="30"/>
+    </row>
+    <row r="95" spans="2:14">
+      <c r="B95" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Artis</v>
+      </c>
+      <c r="I95" s="30"/>
+    </row>
+    <row r="96" spans="2:14">
+      <c r="B96" t="str">
+        <v>SQ04612</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Spraberry</v>
+      </c>
+      <c r="I96" s="30"/>
+    </row>
+    <row r="97" spans="2:9">
+      <c r="B97" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Shattesh</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Utpat</v>
+      </c>
+      <c r="I97" s="30"/>
+    </row>
+    <row r="98" spans="2:9">
+      <c r="B98" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Sawini</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Chandan</v>
+      </c>
+      <c r="I98" s="30"/>
+    </row>
+    <row r="99" spans="2:9">
+      <c r="B99" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="I99" s="30"/>
+    </row>
+    <row r="100" spans="2:9">
+      <c r="B100" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="I100" s="30"/>
+    </row>
+    <row r="101" spans="2:9">
+      <c r="B101" t="str">
+        <v>TN04892</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Wolstenholme</v>
+      </c>
+      <c r="I101" s="30"/>
+    </row>
+    <row r="102" spans="2:9">
+      <c r="B102" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Raghavanpillai</v>
+      </c>
+      <c r="I102" s="30"/>
+    </row>
+    <row r="103" spans="2:9">
+      <c r="B103" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Linford</v>
+      </c>
+      <c r="I103" s="30"/>
+    </row>
+    <row r="104" spans="2:9">
+      <c r="B104" t="str">
+        <v>VT02417</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Evangelina</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Lergan</v>
+      </c>
+      <c r="I104" s="30"/>
+    </row>
+    <row r="105" spans="2:9">
+      <c r="B105" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="I105" s="30"/>
+    </row>
+    <row r="106" spans="2:9">
+      <c r="B106" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="I106" s="30"/>
+    </row>
+    <row r="107" spans="2:9">
+      <c r="B107" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Colbeck</v>
+      </c>
+      <c r="I107" s="30"/>
+    </row>
+    <row r="108" spans="2:9">
+      <c r="B108" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="I108" s="30"/>
+    </row>
+    <row r="109" spans="2:9">
+      <c r="B109" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="I109" s="30"/>
+    </row>
+    <row r="110" spans="2:9">
+      <c r="B110" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Biles</v>
+      </c>
+      <c r="I110" s="30"/>
+    </row>
+    <row r="111" spans="2:9">
+      <c r="I111" s="30"/>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="28" t="str" cm="1">
+        <f t="array" ref="B114:D114">_xlfn.CHOOSECOLS(staff[#Headers],1,2,8)</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C114" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D114" s="28" t="str">
+        <v>Start Date</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" t="str" cm="1">
+        <f t="array" ref="B115:D136">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS(staff[],1,2,8),MONTH(staff[Start Date])=3)</f>
+        <v>PR00746</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D115" s="30">
+        <v>43908</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="D116" s="30">
+        <v>44285</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" t="str">
+        <v>SQ00022</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Carlin</v>
+      </c>
+      <c r="D117" s="30">
+        <v>43914</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="D118" s="30">
+        <v>43164</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D119" s="30">
+        <v>43550</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" t="str">
+        <v>SQ03112</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Kantimoy</v>
+      </c>
+      <c r="D120" s="30">
+        <v>43920</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="D121" s="30">
+        <v>43899</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" t="str">
+        <v>SQ04612</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="D122" s="30">
+        <v>43902</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Shattesh</v>
+      </c>
+      <c r="D123" s="30">
+        <v>43916</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Sawini</v>
+      </c>
+      <c r="D124" s="30">
+        <v>43916</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D125" s="30">
+        <v>44277</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="D126" s="30">
+        <v>44277</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" t="str">
+        <v>TN04892</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="D127" s="30">
+        <v>43180</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D128" s="30">
+        <v>43902</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="D129" s="30">
+        <v>43164</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" t="str">
+        <v>VT02417</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Evangelina</v>
+      </c>
+      <c r="D130" s="30">
+        <v>43171</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D131" s="30">
+        <v>44270</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="D132" s="30">
+        <v>44270</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="D133" s="30">
+        <v>44285</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D134" s="30">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="D135" s="30">
+        <v>43895</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="D136" s="30">
+        <v>43171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BDD781A-F91A-41D9-A63E-58DF3A36D552}">
+  <dimension ref="B3:N49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8">
+      <c r="F3" s="41"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="28" t="s">
+        <v>791</v>
+      </c>
+      <c r="C4" s="28">
+        <f>COUNTA(staff[Emp ID])</f>
+        <v>260</v>
+      </c>
+      <c r="D4" s="40">
+        <f>AVERAGE(staff[Salary])</f>
+        <v>73861.325230769246</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="40">
+        <f>MAX(staff[Salary])</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>768</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>792</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>793</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>773</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>794</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="str" cm="1">
+        <f t="array" ref="B7:B18">_xlfn._xlws.SORT(_xlfn.UNIQUE(staff[Department]))</f>
+        <v>Accounting</v>
+      </c>
+      <c r="C7" cm="1">
+        <f t="array" ref="C7:C18">COUNTIFS(staff[Department],_xlfn.ANCHORARRAY(B7))</f>
+        <v>26</v>
+      </c>
+      <c r="D7" s="42" cm="1">
+        <f t="array" ref="D7:D18">AVERAGEIFS(staff[Salary],staff[Department],_xlfn.ANCHORARRAY(B7))</f>
+        <v>69806.945769230777</v>
+      </c>
+      <c r="E7" s="42" cm="1">
+        <f t="array" ref="E7:E18">_xlfn.ANCHORARRAY(D7)-D4</f>
+        <v>-4054.3794615384686</v>
+      </c>
+      <c r="F7" s="42" cm="1">
+        <f t="array" ref="F7:F18">_xlfn.MAXIFS(staff[Salary],staff[Department],_xlfn.ANCHORARRAY(B7))</f>
+        <v>119022.49</v>
+      </c>
+      <c r="G7" s="44" cm="1">
+        <f t="array" ref="G7:G18">_xlfn.MAP(_xlfn.ANCHORARRAY(B7),_xlfn.LAMBDA(_xlpm.x,MEDIAN(_xlfn._xlws.FILTER(staff[Salary],staff[Department]=_xlpm.x))))</f>
+        <v>69025.614999999991</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" ref="H7:H18">COUNTIFS(staff[Department],_xlfn.ANCHORARRAY(B7),staff[Gender],"Female")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8" s="42">
+        <v>79781.805769230778</v>
+      </c>
+      <c r="E8" s="42">
+        <v>5920.480538461532</v>
+      </c>
+      <c r="F8" s="42">
+        <v>110042.37</v>
+      </c>
+      <c r="G8" s="44">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="C9">
+        <v>26</v>
+      </c>
+      <c r="D9" s="42">
+        <v>81976.441923076913</v>
+      </c>
+      <c r="E9" s="42">
+        <v>8115.1166923076671</v>
+      </c>
+      <c r="F9" s="42">
+        <v>120000</v>
+      </c>
+      <c r="G9" s="44">
+        <v>85332.304999999993</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="C10">
+        <v>22</v>
+      </c>
+      <c r="D10" s="42">
+        <v>73109.377727272746</v>
+      </c>
+      <c r="E10" s="43">
+        <v>-751.94750349649985</v>
+      </c>
+      <c r="F10" s="42">
+        <v>103494.94</v>
+      </c>
+      <c r="G10" s="44">
+        <v>73182.794999999998</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="C11">
+        <v>21</v>
+      </c>
+      <c r="D11" s="42">
+        <v>67242.51761904762</v>
+      </c>
+      <c r="E11" s="43">
+        <v>-6618.807611721626</v>
+      </c>
+      <c r="F11" s="42">
+        <v>113747.56</v>
+      </c>
+      <c r="G11" s="44">
+        <v>66572.58</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12" s="42">
+        <v>64441.299999999996</v>
+      </c>
+      <c r="E12" s="43">
+        <v>-9420.0252307692499</v>
+      </c>
+      <c r="F12" s="42">
+        <v>104903.79</v>
+      </c>
+      <c r="G12" s="44">
+        <v>66961.489999999991</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13" s="42">
+        <v>75179.064482758593</v>
+      </c>
+      <c r="E13" s="43">
+        <v>1317.7392519893474</v>
+      </c>
+      <c r="F13" s="42">
+        <v>115191.38</v>
+      </c>
+      <c r="G13" s="44">
+        <v>72502.61</v>
+      </c>
+      <c r="H13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="C14">
+        <v>18</v>
+      </c>
+      <c r="D14" s="42">
+        <v>66910.765555555554</v>
+      </c>
+      <c r="E14" s="43">
+        <v>-6950.5596752136917</v>
+      </c>
+      <c r="F14" s="42">
+        <v>99683.67</v>
+      </c>
+      <c r="G14" s="44">
+        <v>65995.375</v>
+      </c>
+      <c r="H14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="C15">
+        <v>18</v>
+      </c>
+      <c r="D15" s="42">
+        <v>71897.095555555556</v>
+      </c>
+      <c r="E15" s="42">
+        <v>-1964.2296752136899</v>
+      </c>
+      <c r="F15" s="42">
+        <v>102129.37</v>
+      </c>
+      <c r="G15" s="44">
+        <v>79396.654999999999</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" t="str">
+        <v>Services</v>
+      </c>
+      <c r="C16">
+        <v>21</v>
+      </c>
+      <c r="D16" s="42">
+        <v>74673.974761904756</v>
+      </c>
+      <c r="E16" s="42">
+        <v>812.64953113551019</v>
+      </c>
+      <c r="F16" s="42">
+        <v>120000</v>
+      </c>
+      <c r="G16" s="44">
+        <v>77096.05</v>
+      </c>
+      <c r="H16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" t="str">
+        <v>Support</v>
+      </c>
+      <c r="C17">
+        <v>17</v>
+      </c>
+      <c r="D17" s="42">
+        <v>66432.455882352937</v>
+      </c>
+      <c r="E17" s="43">
+        <v>-7428.8693484163086</v>
+      </c>
+      <c r="F17" s="42">
+        <v>104802.63</v>
+      </c>
+      <c r="G17" s="44">
+        <v>61214.26</v>
+      </c>
+      <c r="H17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" t="str">
+        <v>Training</v>
+      </c>
+      <c r="C18">
+        <v>24</v>
+      </c>
+      <c r="D18" s="42">
+        <v>83883.965000000011</v>
+      </c>
+      <c r="E18" s="43">
+        <v>10022.639769230766</v>
+      </c>
+      <c r="F18" s="42">
+        <v>116767.63</v>
+      </c>
+      <c r="G18" s="44">
+        <v>89569.44</v>
+      </c>
+      <c r="H18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="G19" s="28" t="s">
+        <v>796</v>
+      </c>
+      <c r="H19">
+        <f>SUM(H7:H18)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="28" t="str" cm="1">
+        <f t="array" ref="B22:N22">staff[#Headers]</f>
+        <v>Emp ID</v>
+      </c>
+      <c r="C22" s="28" t="str">
+        <v>First Name</v>
+      </c>
+      <c r="D22" s="28" t="str">
+        <v>Last Name</v>
+      </c>
+      <c r="E22" s="28" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="F22" s="28" t="str">
+        <v>Department</v>
+      </c>
+      <c r="G22" s="28" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="H22" s="28" t="str">
+        <v>Salary Bucket</v>
+      </c>
+      <c r="I22" s="28" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="J22" s="28" t="str">
+        <v>FTE</v>
+      </c>
+      <c r="K22" s="28" t="str">
+        <v>Employee type</v>
+      </c>
+      <c r="L22" s="28" t="str">
+        <v>Work location</v>
+      </c>
+      <c r="M22" s="28" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="N22" s="28" t="str">
+        <v>Work Type</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" t="str" cm="1">
+        <f t="array" ref="B23:N48">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(staff[], staff[Department]="Accounting"),6,1)</f>
+        <v>PR01055</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Devasree</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Fullara</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G23" s="44">
+        <v>35936.31</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I23">
+        <v>43241</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M23">
+        <v>6.0904109589041093</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" t="str">
+        <v>PR01956</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Jamesy</v>
+      </c>
+      <c r="D24" t="str">
+        <v>O'Ferris</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G24" s="44">
+        <v>36547.58</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I24">
+        <v>43416</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M24">
+        <v>5.6109589041095891</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" t="str">
+        <v>PR01956</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Jamesy</v>
+      </c>
+      <c r="D25" t="str">
+        <v>O'Ferris</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G25" s="44">
+        <v>36547.58</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I25">
+        <v>43416</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M25">
+        <v>5.6109589041095891</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" t="str">
+        <v>VT04273</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Brad</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Gumb</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G26" s="44">
+        <v>38825.18</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I26">
+        <v>43696</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M26">
+        <v>4.8438356164383558</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" t="str">
+        <v>SQ02223</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Pippy</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Shepperd</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G27" s="44">
+        <v>44845.33</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I27">
+        <v>43277</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="M27">
+        <v>5.9917808219178079</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Kolakovic</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G28" s="44">
+        <v>49915.14</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I28">
+        <v>43550</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M28">
+        <v>5.2438356164383562</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" t="str">
+        <v>VT03849</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Leonidas</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Cavaney</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G29" s="44">
+        <v>52246.29</v>
+      </c>
+      <c r="H29" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I29">
+        <v>43573</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M29">
+        <v>5.1808219178082195</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" t="str">
+        <v>SQ02424</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Kevalkumar</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Solanki</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G30" s="44">
+        <v>52270.22</v>
+      </c>
+      <c r="H30" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I30">
+        <v>43521</v>
+      </c>
+      <c r="J30">
+        <v>0.3</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M30">
+        <v>5.3232876712328769</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" t="str">
+        <v>PR00882</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Jill</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Shipsey</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G31" s="44">
+        <v>52963.65</v>
+      </c>
+      <c r="H31" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I31">
+        <v>44288</v>
+      </c>
+      <c r="J31">
+        <v>0.3</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M31">
+        <v>3.2219178082191782</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" t="str">
+        <v>VT01092</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Tabby</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Astall</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G32" s="44">
+        <v>57419.35</v>
+      </c>
+      <c r="H32" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I32">
+        <v>43305</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M32">
+        <v>5.9150684931506845</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33" t="str">
+        <v>TN01701</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Yves</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Pawlik</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G33" s="44">
+        <v>57925.91</v>
+      </c>
+      <c r="H33" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I33">
+        <v>43572</v>
+      </c>
+      <c r="J33">
+        <v>0.5</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M33">
+        <v>5.183561643835616</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" t="str">
+        <v>TN01028</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Alicea</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Pudsall</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G34" s="44">
+        <v>67633.850000000006</v>
+      </c>
+      <c r="H34" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I34">
+        <v>43340</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M34">
+        <v>5.8191780821917805</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" t="str">
+        <v>SQ03321</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Gradey</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Litton</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G35" s="44">
+        <v>68887.839999999997</v>
+      </c>
+      <c r="H35" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I35">
+        <v>43297</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M35">
+        <v>5.9369863013698634</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" t="str">
+        <v>TN02570</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Grady</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Rochelle</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G36" s="44">
+        <v>69163.39</v>
+      </c>
+      <c r="H36" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I36">
+        <v>43397</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M36">
+        <v>5.6630136986301371</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
+      <c r="B37" t="str">
+        <v>TN02570</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Grady</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Rochelle</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G37" s="44">
+        <v>69163.39</v>
+      </c>
+      <c r="H37" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I37">
+        <v>43397</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M37">
+        <v>5.6630136986301371</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
+      <c r="B38" t="str">
+        <v>VT02374</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Delphine</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Jewis</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G38" s="44">
+        <v>71823.56</v>
+      </c>
+      <c r="H38" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I38">
+        <v>43374</v>
+      </c>
+      <c r="J38">
+        <v>0.3</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M38">
+        <v>5.7260273972602738</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
+      <c r="B39" t="str">
+        <v>VT02374</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Delphine</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Jewis</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G39" s="44">
+        <v>71823.56</v>
+      </c>
+      <c r="H39" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I39">
+        <v>43374</v>
+      </c>
+      <c r="J39">
+        <v>0.3</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M39">
+        <v>5.7260273972602738</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
+      <c r="B40" t="str">
+        <v>VT01610</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Dhruv</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Manjunath</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G40" s="44">
+        <v>76303.820000000007</v>
+      </c>
+      <c r="H40" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I40">
+        <v>43458</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M40">
+        <v>5.4958904109589044</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
+      <c r="B41" t="str">
+        <v>VT01610</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Kunja</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Prashanta</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G41" s="44">
+        <v>76303.820000000007</v>
+      </c>
+      <c r="H41" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I41">
+        <v>43458</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M41">
+        <v>5.4958904109589044</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
+      <c r="B42" t="str">
+        <v>PR01211</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Enoch</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Dowrey</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G42" s="44">
+        <v>91645.04</v>
+      </c>
+      <c r="H42" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I42">
+        <v>44223</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M42">
+        <v>3.4</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
+      <c r="B43" t="str">
+        <v>PR02140</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Anjushri</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Chandiramani</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G43" s="44">
+        <v>95954.02</v>
+      </c>
+      <c r="H43" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I43">
+        <v>43567</v>
+      </c>
+      <c r="J43">
+        <v>0.3</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="M43">
+        <v>5.1972602739726028</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
+      <c r="B44" t="str">
+        <v>TN02377</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Anjela</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Spancock</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Need to check</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G44" s="44">
+        <v>98012.63</v>
+      </c>
+      <c r="H44" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I44">
+        <v>43780</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M44">
+        <v>4.6136986301369864</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
+      <c r="B45" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Raghavanpillai</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G45" s="44">
+        <v>102515.81</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I45">
+        <v>43902</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M45">
+        <v>4.279452054794521</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
+      <c r="B46" t="str">
+        <v>SQ03476</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Ramalingam</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Kothapeta</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Need to check</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G46" s="44">
+        <v>107107.6</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I46">
+        <v>43325</v>
+      </c>
+      <c r="J46">
+        <v>0.9</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M46">
+        <v>5.86027397260274</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
+      <c r="B47" t="str">
+        <v>PR00746</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G47" s="44">
+        <v>114177.23</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I47">
+        <v>43908</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M47">
+        <v>4.2630136986301368</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
+      <c r="B48" t="str">
+        <v>PR03886</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Edd</v>
+      </c>
+      <c r="D48" t="str">
+        <v>MacKnockiter</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G48" s="44">
+        <v>119022.49</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I48">
+        <v>44431</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M48">
+        <v>2.8301369863013699</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7">
+      <c r="F49">
+        <f>COUNTIF(F23:F48, "Accounting")</f>
+        <v>26</v>
+      </c>
+      <c r="G49">
+        <f>COUNT(G23:G48)</f>
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E7:E18">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F62BC468-49DA-4ED9-9010-343A55DAD995}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F62BC468-49DA-4ED9-9010-343A55DAD995}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E7:E18</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE182796-6443-4558-9B87-909B73329DFC}">
   <dimension ref="A1:O267"/>
@@ -4728,7 +10008,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1">
+    <row r="8" spans="1:15">
       <c r="C8" t="s">
         <v>42</v>
       </c>
@@ -4769,7 +10049,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1">
+    <row r="9" spans="1:15">
       <c r="C9" t="s">
         <v>51</v>
       </c>
@@ -4892,7 +10172,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1">
+    <row r="12" spans="1:15">
       <c r="C12" t="s">
         <v>61</v>
       </c>
@@ -4933,7 +10213,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1">
+    <row r="13" spans="1:15">
       <c r="C13" t="s">
         <v>68</v>
       </c>
@@ -4974,7 +10254,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1">
+    <row r="14" spans="1:15">
       <c r="C14" t="s">
         <v>72</v>
       </c>
@@ -5015,7 +10295,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1">
+    <row r="15" spans="1:15">
       <c r="C15" t="s">
         <v>75</v>
       </c>
@@ -5056,7 +10336,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1">
+    <row r="16" spans="1:15">
       <c r="C16" t="s">
         <v>79</v>
       </c>
@@ -5097,7 +10377,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="3:15" hidden="1">
+    <row r="17" spans="3:15">
       <c r="C17" t="s">
         <v>83</v>
       </c>
@@ -5138,7 +10418,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="3:15" hidden="1">
+    <row r="18" spans="3:15">
       <c r="C18" t="s">
         <v>87</v>
       </c>
@@ -5179,7 +10459,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="3:15" hidden="1">
+    <row r="19" spans="3:15">
       <c r="C19" t="s">
         <v>90</v>
       </c>
@@ -5220,7 +10500,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:15" hidden="1">
+    <row r="20" spans="3:15">
       <c r="C20" t="s">
         <v>94</v>
       </c>
@@ -5261,7 +10541,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="3:15" hidden="1">
+    <row r="21" spans="3:15">
       <c r="C21" t="s">
         <v>98</v>
       </c>
@@ -5302,7 +10582,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:15" hidden="1">
+    <row r="22" spans="3:15">
       <c r="C22" t="s">
         <v>102</v>
       </c>
@@ -5343,7 +10623,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="3:15" hidden="1">
+    <row r="23" spans="3:15">
       <c r="C23" t="s">
         <v>106</v>
       </c>
@@ -5384,7 +10664,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="3:15" hidden="1">
+    <row r="24" spans="3:15">
       <c r="C24" t="s">
         <v>110</v>
       </c>
@@ -5425,7 +10705,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="3:15" hidden="1">
+    <row r="25" spans="3:15">
       <c r="C25" t="s">
         <v>113</v>
       </c>
@@ -5466,7 +10746,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="3:15" hidden="1">
+    <row r="26" spans="3:15">
       <c r="C26" t="s">
         <v>117</v>
       </c>
@@ -5507,7 +10787,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="3:15" hidden="1">
+    <row r="27" spans="3:15">
       <c r="C27" t="s">
         <v>120</v>
       </c>
@@ -5548,7 +10828,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="3:15" hidden="1">
+    <row r="28" spans="3:15">
       <c r="C28" t="s">
         <v>124</v>
       </c>
@@ -5589,7 +10869,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="3:15" hidden="1">
+    <row r="29" spans="3:15">
       <c r="C29" t="s">
         <v>127</v>
       </c>
@@ -5630,7 +10910,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="3:15" hidden="1">
+    <row r="30" spans="3:15">
       <c r="C30" t="s">
         <v>130</v>
       </c>
@@ -5671,7 +10951,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="3:15" hidden="1">
+    <row r="31" spans="3:15">
       <c r="C31" t="s">
         <v>133</v>
       </c>
@@ -5712,7 +10992,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="3:15" hidden="1">
+    <row r="32" spans="3:15">
       <c r="C32" t="s">
         <v>133</v>
       </c>
@@ -5753,7 +11033,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="3:15" hidden="1">
+    <row r="33" spans="3:15">
       <c r="C33" t="s">
         <v>136</v>
       </c>
@@ -5794,7 +11074,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:15" hidden="1">
+    <row r="34" spans="3:15">
       <c r="C34" t="s">
         <v>139</v>
       </c>
@@ -5835,7 +11115,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="3:15" hidden="1">
+    <row r="35" spans="3:15">
       <c r="C35" t="s">
         <v>142</v>
       </c>
@@ -5876,7 +11156,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="3:15" hidden="1">
+    <row r="36" spans="3:15">
       <c r="C36" t="s">
         <v>146</v>
       </c>
@@ -5917,7 +11197,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:15" hidden="1">
+    <row r="37" spans="3:15">
       <c r="C37" t="s">
         <v>149</v>
       </c>
@@ -5958,7 +11238,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="3:15" hidden="1">
+    <row r="38" spans="3:15">
       <c r="C38" t="s">
         <v>152</v>
       </c>
@@ -5999,7 +11279,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="3:15" hidden="1">
+    <row r="39" spans="3:15">
       <c r="C39" t="s">
         <v>156</v>
       </c>
@@ -6040,7 +11320,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="3:15" hidden="1">
+    <row r="40" spans="3:15">
       <c r="C40" t="s">
         <v>159</v>
       </c>
@@ -6081,7 +11361,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="3:15" hidden="1">
+    <row r="41" spans="3:15">
       <c r="C41" t="s">
         <v>162</v>
       </c>
@@ -6122,7 +11402,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="3:15" hidden="1">
+    <row r="42" spans="3:15">
       <c r="C42" t="s">
         <v>165</v>
       </c>
@@ -6163,7 +11443,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="3:15" hidden="1">
+    <row r="43" spans="3:15">
       <c r="C43" t="s">
         <v>168</v>
       </c>
@@ -6204,7 +11484,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="3:15" hidden="1">
+    <row r="44" spans="3:15">
       <c r="C44" t="s">
         <v>171</v>
       </c>
@@ -6245,7 +11525,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="3:15" hidden="1">
+    <row r="45" spans="3:15">
       <c r="C45" t="s">
         <v>174</v>
       </c>
@@ -6286,7 +11566,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="3:15" hidden="1">
+    <row r="46" spans="3:15">
       <c r="C46" t="s">
         <v>177</v>
       </c>
@@ -6327,7 +11607,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="3:15" hidden="1">
+    <row r="47" spans="3:15">
       <c r="C47" t="s">
         <v>180</v>
       </c>
@@ -6368,7 +11648,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="3:15" hidden="1">
+    <row r="48" spans="3:15">
       <c r="C48" t="s">
         <v>183</v>
       </c>
@@ -6409,7 +11689,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="3:15" hidden="1">
+    <row r="49" spans="3:15">
       <c r="C49" t="s">
         <v>186</v>
       </c>
@@ -6450,7 +11730,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="3:15" hidden="1">
+    <row r="50" spans="3:15">
       <c r="C50" t="s">
         <v>189</v>
       </c>
@@ -6491,7 +11771,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="3:15" hidden="1">
+    <row r="51" spans="3:15">
       <c r="C51" t="s">
         <v>192</v>
       </c>
@@ -6532,7 +11812,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="3:15" hidden="1">
+    <row r="52" spans="3:15">
       <c r="C52" t="s">
         <v>192</v>
       </c>
@@ -6573,7 +11853,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="3:15" hidden="1">
+    <row r="53" spans="3:15">
       <c r="C53" t="s">
         <v>197</v>
       </c>
@@ -6614,7 +11894,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="3:15" hidden="1">
+    <row r="54" spans="3:15">
       <c r="C54" t="s">
         <v>200</v>
       </c>
@@ -6655,7 +11935,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="3:15" hidden="1">
+    <row r="55" spans="3:15">
       <c r="C55" t="s">
         <v>203</v>
       </c>
@@ -6696,7 +11976,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="3:15" hidden="1">
+    <row r="56" spans="3:15">
       <c r="C56" t="s">
         <v>206</v>
       </c>
@@ -6778,7 +12058,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="3:15" hidden="1">
+    <row r="58" spans="3:15">
       <c r="C58" t="s">
         <v>210</v>
       </c>
@@ -6819,7 +12099,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="3:15" hidden="1">
+    <row r="59" spans="3:15">
       <c r="C59" t="s">
         <v>213</v>
       </c>
@@ -6860,7 +12140,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="3:15" hidden="1">
+    <row r="60" spans="3:15">
       <c r="C60" t="s">
         <v>216</v>
       </c>
@@ -6901,7 +12181,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="3:15" hidden="1">
+    <row r="61" spans="3:15">
       <c r="C61" t="s">
         <v>220</v>
       </c>
@@ -6942,7 +12222,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="3:15" hidden="1">
+    <row r="62" spans="3:15">
       <c r="C62" t="s">
         <v>223</v>
       </c>
@@ -6983,7 +12263,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="3:15" hidden="1">
+    <row r="63" spans="3:15">
       <c r="C63" t="s">
         <v>226</v>
       </c>
@@ -7024,7 +12304,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="3:15" hidden="1">
+    <row r="64" spans="3:15">
       <c r="C64" t="s">
         <v>229</v>
       </c>
@@ -7065,7 +12345,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="3:15" hidden="1">
+    <row r="65" spans="3:15">
       <c r="C65" t="s">
         <v>232</v>
       </c>
@@ -7106,7 +12386,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="3:15" hidden="1">
+    <row r="66" spans="3:15">
       <c r="C66" t="s">
         <v>235</v>
       </c>
@@ -7147,7 +12427,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="3:15" hidden="1">
+    <row r="67" spans="3:15">
       <c r="C67" t="s">
         <v>238</v>
       </c>
@@ -7188,7 +12468,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="3:15" hidden="1">
+    <row r="68" spans="3:15">
       <c r="C68" t="s">
         <v>241</v>
       </c>
@@ -7229,7 +12509,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="3:15" hidden="1">
+    <row r="69" spans="3:15">
       <c r="C69" t="s">
         <v>244</v>
       </c>
@@ -7270,7 +12550,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="3:15" hidden="1">
+    <row r="70" spans="3:15">
       <c r="C70" t="s">
         <v>247</v>
       </c>
@@ -7311,7 +12591,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="3:15" hidden="1">
+    <row r="71" spans="3:15">
       <c r="C71" t="s">
         <v>248</v>
       </c>
@@ -7352,7 +12632,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="3:15" hidden="1">
+    <row r="72" spans="3:15">
       <c r="C72" t="s">
         <v>251</v>
       </c>
@@ -7393,7 +12673,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="3:15" hidden="1">
+    <row r="73" spans="3:15">
       <c r="C73" t="s">
         <v>254</v>
       </c>
@@ -7434,7 +12714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="3:15" hidden="1">
+    <row r="74" spans="3:15">
       <c r="C74" t="s">
         <v>257</v>
       </c>
@@ -7475,7 +12755,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="3:15" hidden="1">
+    <row r="75" spans="3:15">
       <c r="C75" t="s">
         <v>260</v>
       </c>
@@ -7516,7 +12796,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="3:15" hidden="1">
+    <row r="76" spans="3:15">
       <c r="C76" t="s">
         <v>260</v>
       </c>
@@ -7557,7 +12837,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="3:15" hidden="1">
+    <row r="77" spans="3:15">
       <c r="C77" t="s">
         <v>265</v>
       </c>
@@ -7598,7 +12878,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="3:15" hidden="1">
+    <row r="78" spans="3:15">
       <c r="C78" t="s">
         <v>268</v>
       </c>
@@ -7639,7 +12919,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="3:15" hidden="1">
+    <row r="79" spans="3:15">
       <c r="C79" t="s">
         <v>271</v>
       </c>
@@ -7680,7 +12960,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="3:15" hidden="1">
+    <row r="80" spans="3:15">
       <c r="C80" t="s">
         <v>274</v>
       </c>
@@ -7721,7 +13001,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="3:15" hidden="1">
+    <row r="81" spans="3:15">
       <c r="C81" t="s">
         <v>277</v>
       </c>
@@ -7762,7 +13042,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="3:15" hidden="1">
+    <row r="82" spans="3:15">
       <c r="C82" t="s">
         <v>280</v>
       </c>
@@ -7803,7 +13083,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="3:15" hidden="1">
+    <row r="83" spans="3:15">
       <c r="C83" t="s">
         <v>283</v>
       </c>
@@ -7844,7 +13124,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="3:15" hidden="1">
+    <row r="84" spans="3:15">
       <c r="C84" t="s">
         <v>286</v>
       </c>
@@ -7885,7 +13165,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="3:15" hidden="1">
+    <row r="85" spans="3:15">
       <c r="C85" t="s">
         <v>289</v>
       </c>
@@ -7926,7 +13206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="3:15" hidden="1">
+    <row r="86" spans="3:15">
       <c r="C86" t="s">
         <v>292</v>
       </c>
@@ -7967,7 +13247,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="3:15" hidden="1">
+    <row r="87" spans="3:15">
       <c r="C87" t="s">
         <v>295</v>
       </c>
@@ -8008,7 +13288,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="88" spans="3:15" hidden="1">
+    <row r="88" spans="3:15">
       <c r="C88" t="s">
         <v>298</v>
       </c>
@@ -8049,7 +13329,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="89" spans="3:15" hidden="1">
+    <row r="89" spans="3:15">
       <c r="C89" t="s">
         <v>301</v>
       </c>
@@ -8090,7 +13370,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="3:15" hidden="1">
+    <row r="90" spans="3:15">
       <c r="C90" t="s">
         <v>304</v>
       </c>
@@ -8131,7 +13411,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="91" spans="3:15" hidden="1">
+    <row r="91" spans="3:15">
       <c r="C91" t="s">
         <v>304</v>
       </c>
@@ -8172,7 +13452,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="3:15" hidden="1">
+    <row r="92" spans="3:15">
       <c r="C92" t="s">
         <v>309</v>
       </c>
@@ -8213,7 +13493,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="3:15" hidden="1">
+    <row r="93" spans="3:15">
       <c r="C93" t="s">
         <v>309</v>
       </c>
@@ -8254,7 +13534,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="3:15" hidden="1">
+    <row r="94" spans="3:15">
       <c r="C94" t="s">
         <v>312</v>
       </c>
@@ -8295,7 +13575,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="3:15" hidden="1">
+    <row r="95" spans="3:15">
       <c r="C95" t="s">
         <v>315</v>
       </c>
@@ -8336,7 +13616,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="96" spans="3:15" hidden="1">
+    <row r="96" spans="3:15">
       <c r="C96" t="s">
         <v>318</v>
       </c>
@@ -8377,7 +13657,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="3:15" hidden="1">
+    <row r="97" spans="3:15">
       <c r="C97" t="s">
         <v>321</v>
       </c>
@@ -8418,7 +13698,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="3:15" hidden="1">
+    <row r="98" spans="3:15">
       <c r="C98" t="s">
         <v>324</v>
       </c>
@@ -8459,7 +13739,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="3:15" hidden="1">
+    <row r="99" spans="3:15">
       <c r="C99" t="s">
         <v>327</v>
       </c>
@@ -8500,7 +13780,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="3:15" hidden="1">
+    <row r="100" spans="3:15">
       <c r="C100" t="s">
         <v>330</v>
       </c>
@@ -8541,7 +13821,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="3:15" hidden="1">
+    <row r="101" spans="3:15">
       <c r="C101" t="s">
         <v>333</v>
       </c>
@@ -8582,7 +13862,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="3:15" hidden="1">
+    <row r="102" spans="3:15">
       <c r="C102" t="s">
         <v>333</v>
       </c>
@@ -8623,7 +13903,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="103" spans="3:15" hidden="1">
+    <row r="103" spans="3:15">
       <c r="C103" t="s">
         <v>336</v>
       </c>
@@ -8664,7 +13944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="3:15" hidden="1">
+    <row r="104" spans="3:15">
       <c r="C104" t="s">
         <v>339</v>
       </c>
@@ -8705,7 +13985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="3:15" hidden="1">
+    <row r="105" spans="3:15">
       <c r="C105" t="s">
         <v>342</v>
       </c>
@@ -8746,7 +14026,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="106" spans="3:15" hidden="1">
+    <row r="106" spans="3:15">
       <c r="C106" t="s">
         <v>345</v>
       </c>
@@ -8787,7 +14067,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="3:15" hidden="1">
+    <row r="107" spans="3:15">
       <c r="C107" t="s">
         <v>348</v>
       </c>
@@ -8828,7 +14108,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="3:15" hidden="1">
+    <row r="108" spans="3:15">
       <c r="C108" t="s">
         <v>351</v>
       </c>
@@ -8869,7 +14149,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="3:15" hidden="1">
+    <row r="109" spans="3:15">
       <c r="C109" t="s">
         <v>354</v>
       </c>
@@ -8910,7 +14190,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="3:15" hidden="1">
+    <row r="110" spans="3:15">
       <c r="C110" t="s">
         <v>354</v>
       </c>
@@ -8951,7 +14231,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="111" spans="3:15" hidden="1">
+    <row r="111" spans="3:15">
       <c r="C111" t="s">
         <v>357</v>
       </c>
@@ -8992,7 +14272,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="3:15" hidden="1">
+    <row r="112" spans="3:15">
       <c r="C112" t="s">
         <v>360</v>
       </c>
@@ -9033,7 +14313,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="3:15" hidden="1">
+    <row r="113" spans="3:15">
       <c r="C113" t="s">
         <v>363</v>
       </c>
@@ -9074,7 +14354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="3:15" hidden="1">
+    <row r="114" spans="3:15">
       <c r="C114" t="s">
         <v>366</v>
       </c>
@@ -9115,7 +14395,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="3:15" hidden="1">
+    <row r="115" spans="3:15">
       <c r="C115" t="s">
         <v>366</v>
       </c>
@@ -9156,7 +14436,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" spans="3:15" hidden="1">
+    <row r="116" spans="3:15">
       <c r="C116" t="s">
         <v>369</v>
       </c>
@@ -9197,7 +14477,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="3:15" hidden="1">
+    <row r="117" spans="3:15">
       <c r="C117" t="s">
         <v>372</v>
       </c>
@@ -9238,7 +14518,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="3:15" hidden="1">
+    <row r="118" spans="3:15">
       <c r="C118" t="s">
         <v>375</v>
       </c>
@@ -9279,7 +14559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="119" spans="3:15" hidden="1">
+    <row r="119" spans="3:15">
       <c r="C119" t="s">
         <v>378</v>
       </c>
@@ -9320,7 +14600,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="3:15" hidden="1">
+    <row r="120" spans="3:15">
       <c r="C120" t="s">
         <v>381</v>
       </c>
@@ -9361,7 +14641,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="3:15" hidden="1">
+    <row r="121" spans="3:15">
       <c r="C121" t="s">
         <v>384</v>
       </c>
@@ -9402,7 +14682,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="3:15" hidden="1">
+    <row r="122" spans="3:15">
       <c r="C122" t="s">
         <v>387</v>
       </c>
@@ -9443,7 +14723,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="3:15" hidden="1">
+    <row r="123" spans="3:15">
       <c r="C123" t="s">
         <v>390</v>
       </c>
@@ -9484,7 +14764,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="3:15" hidden="1">
+    <row r="124" spans="3:15">
       <c r="C124" t="s">
         <v>393</v>
       </c>
@@ -9525,7 +14805,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125" spans="3:15" hidden="1">
+    <row r="125" spans="3:15">
       <c r="C125" t="s">
         <v>396</v>
       </c>
@@ -9566,7 +14846,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="126" spans="3:15" hidden="1">
+    <row r="126" spans="3:15">
       <c r="C126" t="s">
         <v>399</v>
       </c>
@@ -9607,7 +14887,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="3:15" hidden="1">
+    <row r="127" spans="3:15">
       <c r="C127" t="s">
         <v>402</v>
       </c>
@@ -9648,7 +14928,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="3:15" hidden="1">
+    <row r="128" spans="3:15">
       <c r="C128" t="s">
         <v>405</v>
       </c>
@@ -9689,7 +14969,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="129" spans="3:15" hidden="1">
+    <row r="129" spans="3:15">
       <c r="C129" t="s">
         <v>408</v>
       </c>
@@ -9730,7 +15010,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="3:15" hidden="1">
+    <row r="130" spans="3:15">
       <c r="C130" t="s">
         <v>411</v>
       </c>
@@ -9771,7 +15051,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="3:15" hidden="1">
+    <row r="131" spans="3:15">
       <c r="C131" t="s">
         <v>414</v>
       </c>
@@ -9812,7 +15092,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="3:15" hidden="1">
+    <row r="132" spans="3:15">
       <c r="C132" t="s">
         <v>417</v>
       </c>
@@ -9853,7 +15133,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="3:15" hidden="1">
+    <row r="133" spans="3:15">
       <c r="C133" t="s">
         <v>420</v>
       </c>
@@ -9894,7 +15174,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="134" spans="3:15" hidden="1">
+    <row r="134" spans="3:15">
       <c r="C134" t="s">
         <v>420</v>
       </c>
@@ -9935,7 +15215,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="135" spans="3:15" hidden="1">
+    <row r="135" spans="3:15">
       <c r="C135" t="s">
         <v>425</v>
       </c>
@@ -9976,7 +15256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="3:15" hidden="1">
+    <row r="136" spans="3:15">
       <c r="C136" t="s">
         <v>428</v>
       </c>
@@ -10017,7 +15297,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="137" spans="3:15" hidden="1">
+    <row r="137" spans="3:15">
       <c r="C137" t="s">
         <v>431</v>
       </c>
@@ -10058,7 +15338,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="138" spans="3:15" hidden="1">
+    <row r="138" spans="3:15">
       <c r="C138" t="s">
         <v>434</v>
       </c>
@@ -10099,7 +15379,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="3:15" hidden="1">
+    <row r="139" spans="3:15">
       <c r="C139" t="s">
         <v>437</v>
       </c>
@@ -10140,7 +15420,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="3:15" hidden="1">
+    <row r="140" spans="3:15">
       <c r="C140" t="s">
         <v>440</v>
       </c>
@@ -10181,7 +15461,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="3:15" hidden="1">
+    <row r="141" spans="3:15">
       <c r="C141" t="s">
         <v>443</v>
       </c>
@@ -10222,7 +15502,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="3:15" hidden="1">
+    <row r="142" spans="3:15">
       <c r="C142" t="s">
         <v>446</v>
       </c>
@@ -10263,7 +15543,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="3:15" hidden="1">
+    <row r="143" spans="3:15">
       <c r="C143" t="s">
         <v>446</v>
       </c>
@@ -10304,7 +15584,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="3:15" hidden="1">
+    <row r="144" spans="3:15">
       <c r="C144" t="s">
         <v>449</v>
       </c>
@@ -10345,7 +15625,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="3:15" hidden="1">
+    <row r="145" spans="3:15">
       <c r="C145" t="s">
         <v>452</v>
       </c>
@@ -10386,7 +15666,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="146" spans="3:15" hidden="1">
+    <row r="146" spans="3:15">
       <c r="C146" t="s">
         <v>455</v>
       </c>
@@ -10427,7 +15707,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="3:15" hidden="1">
+    <row r="147" spans="3:15">
       <c r="C147" t="s">
         <v>458</v>
       </c>
@@ -10468,7 +15748,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="148" spans="3:15" hidden="1">
+    <row r="148" spans="3:15">
       <c r="C148" t="s">
         <v>458</v>
       </c>
@@ -10509,7 +15789,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="149" spans="3:15" hidden="1">
+    <row r="149" spans="3:15">
       <c r="C149" t="s">
         <v>463</v>
       </c>
@@ -10550,7 +15830,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="3:15" hidden="1">
+    <row r="150" spans="3:15">
       <c r="C150" t="s">
         <v>466</v>
       </c>
@@ -10591,7 +15871,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="3:15" hidden="1">
+    <row r="151" spans="3:15">
       <c r="C151" t="s">
         <v>469</v>
       </c>
@@ -10632,7 +15912,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="3:15" hidden="1">
+    <row r="152" spans="3:15">
       <c r="C152" t="s">
         <v>472</v>
       </c>
@@ -10673,7 +15953,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="3:15" hidden="1">
+    <row r="153" spans="3:15">
       <c r="C153" t="s">
         <v>475</v>
       </c>
@@ -10714,7 +15994,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="3:15" hidden="1">
+    <row r="154" spans="3:15">
       <c r="C154" t="s">
         <v>475</v>
       </c>
@@ -10755,7 +16035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="3:15" hidden="1">
+    <row r="155" spans="3:15">
       <c r="C155" t="s">
         <v>478</v>
       </c>
@@ -10796,7 +16076,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="3:15" hidden="1">
+    <row r="156" spans="3:15">
       <c r="C156" t="s">
         <v>481</v>
       </c>
@@ -10837,7 +16117,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="3:15" hidden="1">
+    <row r="157" spans="3:15">
       <c r="C157" t="s">
         <v>484</v>
       </c>
@@ -10878,7 +16158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="3:15" hidden="1">
+    <row r="158" spans="3:15">
       <c r="C158" t="s">
         <v>484</v>
       </c>
@@ -10919,7 +16199,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="3:15" hidden="1">
+    <row r="159" spans="3:15">
       <c r="C159" t="s">
         <v>487</v>
       </c>
@@ -10960,7 +16240,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="3:15" hidden="1">
+    <row r="160" spans="3:15">
       <c r="C160" t="s">
         <v>490</v>
       </c>
@@ -11001,7 +16281,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="3:15" hidden="1">
+    <row r="161" spans="3:15">
       <c r="C161" t="s">
         <v>491</v>
       </c>
@@ -11042,7 +16322,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="3:15" hidden="1">
+    <row r="162" spans="3:15">
       <c r="C162" t="s">
         <v>494</v>
       </c>
@@ -11083,7 +16363,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="3:15" hidden="1">
+    <row r="163" spans="3:15">
       <c r="C163" t="s">
         <v>497</v>
       </c>
@@ -11124,7 +16404,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="3:15" hidden="1">
+    <row r="164" spans="3:15">
       <c r="C164" t="s">
         <v>500</v>
       </c>
@@ -11165,7 +16445,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="165" spans="3:15" hidden="1">
+    <row r="165" spans="3:15">
       <c r="C165" t="s">
         <v>503</v>
       </c>
@@ -11206,7 +16486,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166" spans="3:15" hidden="1">
+    <row r="166" spans="3:15">
       <c r="C166" t="s">
         <v>503</v>
       </c>
@@ -11247,7 +16527,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="3:15" hidden="1">
+    <row r="167" spans="3:15">
       <c r="C167" t="s">
         <v>506</v>
       </c>
@@ -11288,7 +16568,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="168" spans="3:15" hidden="1">
+    <row r="168" spans="3:15">
       <c r="C168" t="s">
         <v>506</v>
       </c>
@@ -11329,7 +16609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="169" spans="3:15" hidden="1">
+    <row r="169" spans="3:15">
       <c r="C169" t="s">
         <v>509</v>
       </c>
@@ -11370,7 +16650,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" spans="3:15" hidden="1">
+    <row r="170" spans="3:15">
       <c r="C170" t="s">
         <v>512</v>
       </c>
@@ -11411,7 +16691,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="3:15" hidden="1">
+    <row r="171" spans="3:15">
       <c r="C171" t="s">
         <v>515</v>
       </c>
@@ -11452,7 +16732,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="3:15" hidden="1">
+    <row r="172" spans="3:15">
       <c r="C172" t="s">
         <v>518</v>
       </c>
@@ -11493,7 +16773,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="173" spans="3:15" hidden="1">
+    <row r="173" spans="3:15">
       <c r="C173" t="s">
         <v>521</v>
       </c>
@@ -11534,7 +16814,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" spans="3:15" hidden="1">
+    <row r="174" spans="3:15">
       <c r="C174" t="s">
         <v>524</v>
       </c>
@@ -11575,7 +16855,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="3:15" hidden="1">
+    <row r="175" spans="3:15">
       <c r="C175" t="s">
         <v>524</v>
       </c>
@@ -11616,7 +16896,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="3:15" hidden="1">
+    <row r="176" spans="3:15">
       <c r="C176" t="s">
         <v>528</v>
       </c>
@@ -11657,7 +16937,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="177" spans="3:15" hidden="1">
+    <row r="177" spans="3:15">
       <c r="C177" t="s">
         <v>532</v>
       </c>
@@ -11698,7 +16978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="3:15" hidden="1">
+    <row r="178" spans="3:15">
       <c r="C178" t="s">
         <v>535</v>
       </c>
@@ -11739,7 +17019,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="3:15" hidden="1">
+    <row r="179" spans="3:15">
       <c r="C179" t="s">
         <v>535</v>
       </c>
@@ -11780,7 +17060,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="3:15" hidden="1">
+    <row r="180" spans="3:15">
       <c r="C180" t="s">
         <v>538</v>
       </c>
@@ -11821,7 +17101,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="3:15" hidden="1">
+    <row r="181" spans="3:15">
       <c r="C181" t="s">
         <v>541</v>
       </c>
@@ -11862,7 +17142,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="3:15" hidden="1">
+    <row r="182" spans="3:15">
       <c r="C182" t="s">
         <v>542</v>
       </c>
@@ -11903,7 +17183,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="3:15" hidden="1">
+    <row r="183" spans="3:15">
       <c r="C183" t="s">
         <v>545</v>
       </c>
@@ -11944,7 +17224,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="3:15" hidden="1">
+    <row r="184" spans="3:15">
       <c r="C184" t="s">
         <v>548</v>
       </c>
@@ -11985,7 +17265,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="3:15" hidden="1">
+    <row r="185" spans="3:15">
       <c r="C185" t="s">
         <v>548</v>
       </c>
@@ -12026,7 +17306,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="3:15" hidden="1">
+    <row r="186" spans="3:15">
       <c r="C186" t="s">
         <v>551</v>
       </c>
@@ -12067,7 +17347,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="3:15" hidden="1">
+    <row r="187" spans="3:15">
       <c r="C187" t="s">
         <v>551</v>
       </c>
@@ -12108,7 +17388,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="3:15" hidden="1">
+    <row r="188" spans="3:15">
       <c r="C188" t="s">
         <v>556</v>
       </c>
@@ -12149,7 +17429,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="3:15" hidden="1">
+    <row r="189" spans="3:15">
       <c r="C189" t="s">
         <v>559</v>
       </c>
@@ -12190,7 +17470,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="3:15" hidden="1">
+    <row r="190" spans="3:15">
       <c r="C190" t="s">
         <v>562</v>
       </c>
@@ -12231,7 +17511,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="3:15" hidden="1">
+    <row r="191" spans="3:15">
       <c r="C191" t="s">
         <v>565</v>
       </c>
@@ -12272,7 +17552,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="3:15" hidden="1">
+    <row r="192" spans="3:15">
       <c r="C192" t="s">
         <v>568</v>
       </c>
@@ -12313,7 +17593,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="193" spans="3:15" hidden="1">
+    <row r="193" spans="3:15">
       <c r="C193" t="s">
         <v>571</v>
       </c>
@@ -12354,7 +17634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="3:15" hidden="1">
+    <row r="194" spans="3:15">
       <c r="C194" t="s">
         <v>574</v>
       </c>
@@ -12395,7 +17675,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="3:15" hidden="1">
+    <row r="195" spans="3:15">
       <c r="C195" t="s">
         <v>574</v>
       </c>
@@ -12436,7 +17716,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="3:15" hidden="1">
+    <row r="196" spans="3:15">
       <c r="C196" t="s">
         <v>576</v>
       </c>
@@ -12477,7 +17757,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="3:15" hidden="1">
+    <row r="197" spans="3:15">
       <c r="C197" t="s">
         <v>579</v>
       </c>
@@ -12518,7 +17798,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="3:15" hidden="1">
+    <row r="198" spans="3:15">
       <c r="C198" t="s">
         <v>582</v>
       </c>
@@ -12559,7 +17839,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="3:15" hidden="1">
+    <row r="199" spans="3:15">
       <c r="C199" t="s">
         <v>585</v>
       </c>
@@ -12600,7 +17880,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="3:15" hidden="1">
+    <row r="200" spans="3:15">
       <c r="C200" t="s">
         <v>588</v>
       </c>
@@ -12641,7 +17921,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="201" spans="3:15" hidden="1">
+    <row r="201" spans="3:15">
       <c r="C201" t="s">
         <v>591</v>
       </c>
@@ -12682,7 +17962,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="202" spans="3:15" hidden="1">
+    <row r="202" spans="3:15">
       <c r="C202" t="s">
         <v>594</v>
       </c>
@@ -12723,7 +18003,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="203" spans="3:15" hidden="1">
+    <row r="203" spans="3:15">
       <c r="C203" t="s">
         <v>596</v>
       </c>
@@ -12764,7 +18044,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="3:15" hidden="1">
+    <row r="204" spans="3:15">
       <c r="C204" t="s">
         <v>599</v>
       </c>
@@ -12805,7 +18085,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="205" spans="3:15" hidden="1">
+    <row r="205" spans="3:15">
       <c r="C205" t="s">
         <v>602</v>
       </c>
@@ -12846,7 +18126,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="206" spans="3:15" hidden="1">
+    <row r="206" spans="3:15">
       <c r="C206" t="s">
         <v>602</v>
       </c>
@@ -12887,7 +18167,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="207" spans="3:15" hidden="1">
+    <row r="207" spans="3:15">
       <c r="C207" t="s">
         <v>605</v>
       </c>
@@ -12928,7 +18208,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="208" spans="3:15" hidden="1">
+    <row r="208" spans="3:15">
       <c r="C208" t="s">
         <v>608</v>
       </c>
@@ -12969,7 +18249,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="209" spans="3:15" hidden="1">
+    <row r="209" spans="3:15">
       <c r="C209" t="s">
         <v>611</v>
       </c>
@@ -13010,7 +18290,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="210" spans="3:15" hidden="1">
+    <row r="210" spans="3:15">
       <c r="C210" t="s">
         <v>614</v>
       </c>
@@ -13051,7 +18331,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="211" spans="3:15" hidden="1">
+    <row r="211" spans="3:15">
       <c r="C211" t="s">
         <v>617</v>
       </c>
@@ -13092,7 +18372,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="212" spans="3:15" hidden="1">
+    <row r="212" spans="3:15">
       <c r="C212" t="s">
         <v>620</v>
       </c>
@@ -13133,7 +18413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="213" spans="3:15" hidden="1">
+    <row r="213" spans="3:15">
       <c r="C213" t="s">
         <v>623</v>
       </c>
@@ -13174,7 +18454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="214" spans="3:15" hidden="1">
+    <row r="214" spans="3:15">
       <c r="C214" t="s">
         <v>626</v>
       </c>
@@ -13215,7 +18495,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="215" spans="3:15" hidden="1">
+    <row r="215" spans="3:15">
       <c r="C215" t="s">
         <v>629</v>
       </c>
@@ -13256,7 +18536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" spans="3:15" hidden="1">
+    <row r="216" spans="3:15">
       <c r="C216" t="s">
         <v>629</v>
       </c>
@@ -13297,7 +18577,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="217" spans="3:15" hidden="1">
+    <row r="217" spans="3:15">
       <c r="C217" t="s">
         <v>634</v>
       </c>
@@ -13338,7 +18618,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="218" spans="3:15" hidden="1">
+    <row r="218" spans="3:15">
       <c r="C218" t="s">
         <v>637</v>
       </c>
@@ -13379,7 +18659,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="219" spans="3:15" hidden="1">
+    <row r="219" spans="3:15">
       <c r="C219" t="s">
         <v>640</v>
       </c>
@@ -13420,7 +18700,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="220" spans="3:15" hidden="1">
+    <row r="220" spans="3:15">
       <c r="C220" t="s">
         <v>643</v>
       </c>
@@ -13461,7 +18741,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="221" spans="3:15" hidden="1">
+    <row r="221" spans="3:15">
       <c r="C221" t="s">
         <v>646</v>
       </c>
@@ -13502,7 +18782,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="3:15" hidden="1">
+    <row r="222" spans="3:15">
       <c r="C222" t="s">
         <v>649</v>
       </c>
@@ -13543,7 +18823,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="3:15" hidden="1">
+    <row r="223" spans="3:15">
       <c r="C223" t="s">
         <v>649</v>
       </c>
@@ -13584,7 +18864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="224" spans="3:15" hidden="1">
+    <row r="224" spans="3:15">
       <c r="C224" t="s">
         <v>652</v>
       </c>
@@ -13625,7 +18905,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="225" spans="3:15" hidden="1">
+    <row r="225" spans="3:15">
       <c r="C225" t="s">
         <v>655</v>
       </c>
@@ -13666,7 +18946,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="226" spans="3:15" hidden="1">
+    <row r="226" spans="3:15">
       <c r="C226" t="s">
         <v>658</v>
       </c>
@@ -13707,7 +18987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="227" spans="3:15" hidden="1">
+    <row r="227" spans="3:15">
       <c r="C227" t="s">
         <v>662</v>
       </c>
@@ -13748,7 +19028,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="3:15" hidden="1">
+    <row r="228" spans="3:15">
       <c r="C228" t="s">
         <v>662</v>
       </c>
@@ -13789,7 +19069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="3:15" hidden="1">
+    <row r="229" spans="3:15">
       <c r="C229" t="s">
         <v>665</v>
       </c>
@@ -13830,7 +19110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="3:15" hidden="1">
+    <row r="230" spans="3:15">
       <c r="C230" t="s">
         <v>668</v>
       </c>
@@ -13871,7 +19151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="3:15" hidden="1">
+    <row r="231" spans="3:15">
       <c r="C231" t="s">
         <v>668</v>
       </c>
@@ -13912,7 +19192,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="3:15" hidden="1">
+    <row r="232" spans="3:15">
       <c r="C232" t="s">
         <v>671</v>
       </c>
@@ -13953,7 +19233,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="233" spans="3:15" hidden="1">
+    <row r="233" spans="3:15">
       <c r="C233" t="s">
         <v>674</v>
       </c>
@@ -13994,7 +19274,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="234" spans="3:15" hidden="1">
+    <row r="234" spans="3:15">
       <c r="C234" t="s">
         <v>677</v>
       </c>
@@ -14035,7 +19315,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="235" spans="3:15" hidden="1">
+    <row r="235" spans="3:15">
       <c r="C235" t="s">
         <v>680</v>
       </c>
@@ -14076,7 +19356,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="236" spans="3:15" hidden="1">
+    <row r="236" spans="3:15">
       <c r="C236" t="s">
         <v>683</v>
       </c>
@@ -14117,7 +19397,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="237" spans="3:15" hidden="1">
+    <row r="237" spans="3:15">
       <c r="C237" t="s">
         <v>686</v>
       </c>
@@ -14158,7 +19438,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="3:15" hidden="1">
+    <row r="238" spans="3:15">
       <c r="C238" t="s">
         <v>689</v>
       </c>
@@ -14199,7 +19479,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="239" spans="3:15" hidden="1">
+    <row r="239" spans="3:15">
       <c r="C239" t="s">
         <v>692</v>
       </c>
@@ -14240,7 +19520,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="3:15" hidden="1">
+    <row r="240" spans="3:15">
       <c r="C240" t="s">
         <v>695</v>
       </c>
@@ -14281,7 +19561,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="3:15" hidden="1">
+    <row r="241" spans="3:15">
       <c r="C241" t="s">
         <v>695</v>
       </c>
@@ -14322,7 +19602,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="3:15" hidden="1">
+    <row r="242" spans="3:15">
       <c r="C242" t="s">
         <v>698</v>
       </c>
@@ -14363,7 +19643,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="243" spans="3:15" hidden="1">
+    <row r="243" spans="3:15">
       <c r="C243" t="s">
         <v>701</v>
       </c>
@@ -14404,7 +19684,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="244" spans="3:15" hidden="1">
+    <row r="244" spans="3:15">
       <c r="C244" t="s">
         <v>701</v>
       </c>
@@ -14445,7 +19725,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="245" spans="3:15" hidden="1">
+    <row r="245" spans="3:15">
       <c r="C245" t="s">
         <v>704</v>
       </c>
@@ -14486,7 +19766,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="246" spans="3:15" hidden="1">
+    <row r="246" spans="3:15">
       <c r="C246" t="s">
         <v>707</v>
       </c>
@@ -14527,7 +19807,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="247" spans="3:15" hidden="1">
+    <row r="247" spans="3:15">
       <c r="C247" t="s">
         <v>710</v>
       </c>
@@ -14568,7 +19848,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="248" spans="3:15" hidden="1">
+    <row r="248" spans="3:15">
       <c r="C248" t="s">
         <v>713</v>
       </c>
@@ -14609,7 +19889,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="249" spans="3:15" hidden="1">
+    <row r="249" spans="3:15">
       <c r="C249" t="s">
         <v>716</v>
       </c>
@@ -14650,7 +19930,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="250" spans="3:15" hidden="1">
+    <row r="250" spans="3:15">
       <c r="C250" t="s">
         <v>719</v>
       </c>
@@ -14691,7 +19971,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="251" spans="3:15" hidden="1">
+    <row r="251" spans="3:15">
       <c r="C251" t="s">
         <v>722</v>
       </c>
@@ -14732,7 +20012,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="252" spans="3:15" hidden="1">
+    <row r="252" spans="3:15">
       <c r="C252" t="s">
         <v>725</v>
       </c>
@@ -14773,7 +20053,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="3:15" hidden="1">
+    <row r="253" spans="3:15">
       <c r="C253" t="s">
         <v>725</v>
       </c>
@@ -14814,7 +20094,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="254" spans="3:15" hidden="1">
+    <row r="254" spans="3:15">
       <c r="C254" t="s">
         <v>728</v>
       </c>
@@ -14855,7 +20135,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="255" spans="3:15" hidden="1">
+    <row r="255" spans="3:15">
       <c r="C255" t="s">
         <v>728</v>
       </c>
@@ -14896,7 +20176,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="256" spans="3:15" hidden="1">
+    <row r="256" spans="3:15">
       <c r="C256" t="s">
         <v>733</v>
       </c>
@@ -14937,7 +20217,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="257" spans="3:15" hidden="1">
+    <row r="257" spans="3:15">
       <c r="C257" t="s">
         <v>736</v>
       </c>
@@ -14978,7 +20258,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="258" spans="3:15" hidden="1">
+    <row r="258" spans="3:15">
       <c r="C258" t="s">
         <v>739</v>
       </c>
@@ -15019,7 +20299,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="259" spans="3:15" hidden="1">
+    <row r="259" spans="3:15">
       <c r="C259" t="s">
         <v>739</v>
       </c>
@@ -15060,7 +20340,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="260" spans="3:15" hidden="1">
+    <row r="260" spans="3:15">
       <c r="C260" t="s">
         <v>744</v>
       </c>
@@ -15101,7 +20381,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="261" spans="3:15" hidden="1">
+    <row r="261" spans="3:15">
       <c r="C261" t="s">
         <v>747</v>
       </c>
@@ -15142,7 +20422,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="262" spans="3:15" hidden="1">
+    <row r="262" spans="3:15">
       <c r="C262" t="s">
         <v>750</v>
       </c>
@@ -15183,7 +20463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="263" spans="3:15" hidden="1">
+    <row r="263" spans="3:15">
       <c r="C263" t="s">
         <v>753</v>
       </c>
@@ -15224,7 +20504,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="264" spans="3:15" hidden="1">
+    <row r="264" spans="3:15">
       <c r="C264" t="s">
         <v>756</v>
       </c>
@@ -15265,7 +20545,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="265" spans="3:15" hidden="1">
+    <row r="265" spans="3:15">
       <c r="C265" t="s">
         <v>759</v>
       </c>
@@ -15306,7 +20586,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="266" spans="3:15" hidden="1">
+    <row r="266" spans="3:15">
       <c r="C266" t="s">
         <v>762</v>
       </c>
@@ -15347,7 +20627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="267" spans="3:15" hidden="1">
+    <row r="267" spans="3:15">
       <c r="C267" t="s">
         <v>765</v>
       </c>
@@ -19173,6 +24453,7 @@
   <cols>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
     <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:3">
